--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,205 +1009,205 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-35.65</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>377379.9841040462</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1013660.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1714683.2</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>1068516.1</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>538423.64</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>646167</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>122584.2964225742</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>157331.23</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-44.30</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>375725.7004341534</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>601605.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1757941.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>985126.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>520887.4</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>772814</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>116266.6717958167</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>194316.58</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>51.37</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,98 +1419,98 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1700302.2</t>
+          <t>1757941.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>512978.0</t>
+          <t>520887.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>284361.66</v>
+        <v>194316.58</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,37 +1608,37 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68184.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1499818.2</t>
+          <t>1700302.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>884156.4</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>505646.14</t>
+          <t>512978.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>615661</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>68932.8917490568</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>333318.44</v>
+        <v>284361.66</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,37 +2039,37 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>56809.0</t>
+          <t>68184.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,74 +2186,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-3.7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>69.63</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>52.20</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>38.6</t>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2558102.0</t>
+          <t>3149560.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>895619.8</t>
+          <t>1499818.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>588449.0</t>
+          <t>884156.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>445840.3</t>
+          <t>505646.14</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>307170</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20862.79288512989</t>
+          <t>68932.8917490568</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>187880.56</v>
+        <v>333318.44</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,22 +2470,22 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29825.0</t>
+          <t>56809.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,27 +2627,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>52.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,33 +2712,33 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>83.32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1229949.0</t>
+          <t>2558102.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>422349.0</t>
+          <t>895619.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>373937.7</t>
+          <t>588449.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>404007.8</t>
+          <t>445840.3</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>307170</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-9504.073928487198</t>
+          <t>20862.79288512989</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>36772.65</v>
+        <v>187880.56</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>56.68</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8372.0</t>
+          <t>29825.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-40.33</t>
+          <t>12.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.96</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-79.91</t>
+          <t>-78.83</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>313411.0</t>
+          <t>1229949.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>212312.8</t>
+          <t>422349.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>355794.3</t>
+          <t>373937.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>384646.18</t>
+          <t>404007.8</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-143481</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-17918.02324077976</t>
+          <t>-9504.073928487198</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-38107</v>
+        <v>36772.65</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6784.0</t>
+          <t>8372.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-40.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>70.49</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>56.83</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>33.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-62.85</t>
+          <t>-44.96</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.65</t>
+          <t>-79.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>248069.0</t>
+          <t>313411.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>204972.0</t>
+          <t>212312.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>365122.0</t>
+          <t>355794.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>387093.56</t>
+          <t>384646.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-160150</t>
+          <t>-143481</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-14247.29989475405</t>
+          <t>-17918.02324077976</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-45516.46</v>
+        <v>-38107</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3691.0</t>
+          <t>6784.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.49</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-70.55</t>
+          <t>-62.85</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-74.14</t>
+          <t>-77.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>128568.0</t>
+          <t>248069.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>268494.6</t>
+          <t>204972.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>360823.1</t>
+          <t>365122.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>393916.32</t>
+          <t>387093.56</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-92328</t>
+          <t>-160150</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8561.997267127586</t>
+          <t>-14247.29989475405</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-47474.89</v>
+        <v>-45516.46</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,37 +4194,37 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5294.0</t>
+          <t>3691.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>23.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>36.37</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-48.39</t>
+          <t>-70.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.58</t>
+          <t>-74.14</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>191748.0</t>
+          <t>128568.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>281278.2</t>
+          <t>268494.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>386543.3</t>
+          <t>360823.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>400565.94</t>
+          <t>393916.32</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-105265</t>
+          <t>-92328</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1486.925046397366</t>
+          <t>-8561.997267127586</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-35773.44</v>
+        <v>-47474.89</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4844.0</t>
+          <t>5294.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-21.14</t>
+          <t>-27.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-30.56</t>
+          <t>-48.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-65.90</t>
+          <t>-69.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>179768.0</t>
+          <t>191748.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>325526.4</t>
+          <t>281278.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>412786.5</t>
+          <t>386543.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>400741.28</t>
+          <t>400565.94</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-87260</t>
+          <t>-105265</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4746.986999508627</t>
+          <t>-1486.925046397366</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-24548.74</v>
+        <v>-35773.44</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7519.0</t>
+          <t>4844.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>-21.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>35.44</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.37</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-63.29</t>
+          <t>-65.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>375725.7004341534</t>
+          <t>377379.9841040462</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>276707.0</t>
+          <t>179768.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>499275.8</t>
+          <t>325526.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>468779.4</t>
+          <t>412786.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>400576.08</t>
+          <t>400741.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>-87260</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>10073.48325772598</t>
+          <t>4746.986999508627</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6353.15</v>
+        <v>-24548.74</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>17.50403921861844</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>10.6667197364473</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-20.17433314793911</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,17 +5567,17 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>232.15</t>
+          <t>230.98</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>229.96</t>
+          <t>230.29</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>435737.0</t>
+          <t>430123.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1189336.42</t>
+          <t>1191948.4</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-61040.47</v>
+        <v>-58802.8</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,27 +5918,27 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>233.28</t>
+          <t>232.15</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>229.57</t>
+          <t>229.96</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>379052.8</t>
+          <t>435737.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1181965.28</t>
+          <t>1189336.42</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-91884.92999999999</v>
+        <v>-61040.47</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,42 +6349,42 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>2120.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,102 +6506,102 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>-5.45</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-6.51</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12.34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>-1.12</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-15.22</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>243.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>-5.46</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>-0.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>225.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>233.52</t>
+          <t>233.28</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>229.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>217.69</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>-1010.12</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-101.04</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>340930.8</t>
+          <t>379052.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>373683.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1178670.4</t>
+          <t>1181965.28</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>-133148.7005222207</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-111817.38</v>
+        <v>-91884.92999999999</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,42 +6780,42 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1462.0</t>
+          <t>1283.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>228.4</t>
+          <t>226.8</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>233.78</t>
+          <t>233.52</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>228.51</t>
+          <t>229.07</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.32</t>
+          <t>217.53</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-259.94</t>
+          <t>-658.29</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-98.41</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>332244.0</t>
+          <t>288867.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>354728.8</t>
+          <t>340930.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>417109.1</t>
+          <t>402140.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1178768.08</t>
+          <t>1178670.4</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-62380</t>
+          <t>-61209</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-145893.7178646864</t>
+          <t>-140651.2043681088</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-116580.69</v>
+        <v>-111817.38</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,42 +7211,42 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1854.0</t>
+          <t>1462.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>228.4</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>234.52</t>
+          <t>233.78</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>227.97</t>
+          <t>228.51</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.08</t>
+          <t>217.32</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-147.83</t>
+          <t>-259.94</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>417173.0</t>
+          <t>332244.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>366152.8</t>
+          <t>354728.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>437954.8</t>
+          <t>417109.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1179346.74</t>
+          <t>1178768.08</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-71802</t>
+          <t>-62380</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-151223.3594609867</t>
+          <t>-145893.7178646864</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-123869.36</v>
+        <v>-116580.69</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,27 +7642,27 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1854.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-22.92</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>230.7</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>235.02</t>
+          <t>234.52</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>227.33</t>
+          <t>227.97</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>216.79</t>
+          <t>217.08</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-112.55</t>
+          <t>-147.83</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-90.52</t>
+          <t>-93.08</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>384077.0</t>
+          <t>417173.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>350952.6</t>
+          <t>366152.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>455306.6</t>
+          <t>437954.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1181440.22</t>
+          <t>1179346.74</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-104354</t>
+          <t>-71802</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-156196.8146667503</t>
+          <t>-151223.3594609867</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-138957.37</v>
+        <v>-123869.36</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,27 +8073,27 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1682.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-22.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>231.9</t>
+          <t>230.7</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>235.82</t>
+          <t>235.02</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>226.62</t>
+          <t>227.33</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>216.79</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-78.04</t>
+          <t>-112.55</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-90.52</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>282293.0</t>
+          <t>384077.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>368314.2</t>
+          <t>350952.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>468032.0</t>
+          <t>455306.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1179822.7</t>
+          <t>1181440.22</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-99717</t>
+          <t>-104354</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-159331.2596895306</t>
+          <t>-156196.8146667503</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-152002.91</v>
+        <v>-138957.37</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,22 +8504,22 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>232.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1569.0</t>
+          <t>1212.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>232.1</t>
+          <t>231.9</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>236.72</t>
+          <t>235.82</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>226.62</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>216.31</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-67.50</t>
+          <t>-78.04</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-87.85</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>357857.0</t>
+          <t>282293.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>463349.8</t>
+          <t>368314.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>497062.0</t>
+          <t>468032.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1178345.28</t>
+          <t>1179822.7</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-33712</t>
+          <t>-99717</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-160663.6876940798</t>
+          <t>-159331.2596895306</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-154305.29</v>
+        <v>-152002.91</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,27 +8935,27 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1569.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>233.2</t>
+          <t>232.1</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>237.9</t>
+          <t>236.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>225.72</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>216.02</t>
+          <t>216.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-63.85</t>
+          <t>-67.50</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-85.48</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>389364.0</t>
+          <t>357857.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>479489.4</t>
+          <t>463349.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>555156.2</t>
+          <t>497062.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1176598.08</t>
+          <t>1178345.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-75666</t>
+          <t>-33712</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-161819.7607951866</t>
+          <t>-160663.6876940798</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-160179.64</v>
+        <v>-154305.29</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,27 +9366,27 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>235.5</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1455.0</t>
+          <t>1682.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>234.5</t>
+          <t>233.2</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>238.55</t>
+          <t>237.9</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>223.89</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>215.81</t>
+          <t>216.02</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-50.02</t>
+          <t>-63.85</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-80.32</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>341172.0</t>
+          <t>389364.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>509756.8</t>
+          <t>479489.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>562917.4</t>
+          <t>555156.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1180828.9</t>
+          <t>1176598.08</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-53160</t>
+          <t>-75666</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-162117.9646334989</t>
+          <t>-161819.7607951866</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-166226.62</v>
+        <v>-160179.64</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,22 +9797,22 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>235.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>231.5</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026.0</t>
+          <t>1455.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>235.4</t>
+          <t>234.5</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>238.78</t>
+          <t>238.55</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>223.02</t>
+          <t>223.89</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>215.59</t>
+          <t>215.81</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-46.40</t>
+          <t>-50.02</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-77.86</t>
+          <t>-80.32</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>904159.8147612156</t>
+          <t>903696.6611271678</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>470885.0</t>
+          <t>341172.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>559660.6</t>
+          <t>509756.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>596693.8</t>
+          <t>562917.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1185015.16</t>
+          <t>1180828.9</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-37033</t>
+          <t>-53160</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-161370.9359088124</t>
+          <t>-162117.9646334989</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-163765.08</v>
+        <v>-166226.62</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>2.487432770684905</t>
+          <t>-2.745441860838094</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-2.733402932351068</t>
+          <t>-2.833748607962057</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>14.60602544451142</t>
+          <t>11.16140863420413</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10318,17 +10318,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>235.0</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>231.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1714683.2</t>
+          <t>1299298.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>538423.64</t>
+          <t>545802.54</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>157331.23</v>
+        <v>87572.06</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1757941.0</t>
+          <t>1714683.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>520887.4</t>
+          <t>538423.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>194316.58</v>
+        <v>157331.23</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,98 +1850,98 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1700302.2</t>
+          <t>1757941.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>512978.0</t>
+          <t>520887.4</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>284361.66</v>
+        <v>194316.58</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>68184.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1499818.2</t>
+          <t>1700302.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>884156.4</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>505646.14</t>
+          <t>512978.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>615661</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>68932.8917490568</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>333318.44</v>
+        <v>284361.66</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56809.0</t>
+          <t>68184.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,74 +2617,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-7.81</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>69.63</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>52.20</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>38.6</t>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2558102.0</t>
+          <t>3149560.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>895619.8</t>
+          <t>1499818.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>588449.0</t>
+          <t>884156.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>445840.3</t>
+          <t>505646.14</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>307170</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20862.79288512989</t>
+          <t>68932.8917490568</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>187880.56</v>
+        <v>333318.44</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29825.0</t>
+          <t>56809.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,27 +3058,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>52.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,33 +3143,33 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>83.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1229949.0</t>
+          <t>2558102.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>422349.0</t>
+          <t>895619.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>373937.7</t>
+          <t>588449.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>404007.8</t>
+          <t>445840.3</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>307170</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-9504.073928487198</t>
+          <t>20862.79288512989</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>36772.65</v>
+        <v>187880.56</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>56.68</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8372.0</t>
+          <t>29825.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-40.33</t>
+          <t>12.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-44.96</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-79.91</t>
+          <t>-78.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>313411.0</t>
+          <t>1229949.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>212312.8</t>
+          <t>422349.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>355794.3</t>
+          <t>373937.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>384646.18</t>
+          <t>404007.8</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-143481</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-17918.02324077976</t>
+          <t>-9504.073928487198</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-38107</v>
+        <v>36772.65</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6784.0</t>
+          <t>8372.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-40.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>70.49</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>56.83</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>33.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-62.85</t>
+          <t>-44.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-77.65</t>
+          <t>-79.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>248069.0</t>
+          <t>313411.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>204972.0</t>
+          <t>212312.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>365122.0</t>
+          <t>355794.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>387093.56</t>
+          <t>384646.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-160150</t>
+          <t>-143481</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-14247.29989475405</t>
+          <t>-17918.02324077976</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-45516.46</v>
+        <v>-38107</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3691.0</t>
+          <t>6784.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.49</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-70.55</t>
+          <t>-62.85</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-74.14</t>
+          <t>-77.65</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>128568.0</t>
+          <t>248069.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>268494.6</t>
+          <t>204972.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>360823.1</t>
+          <t>365122.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>393916.32</t>
+          <t>387093.56</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-92328</t>
+          <t>-160150</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8561.997267127586</t>
+          <t>-14247.29989475405</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-47474.89</v>
+        <v>-45516.46</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5294.0</t>
+          <t>3691.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>36.37</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-48.39</t>
+          <t>-70.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.58</t>
+          <t>-74.14</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>191748.0</t>
+          <t>128568.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>281278.2</t>
+          <t>268494.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>386543.3</t>
+          <t>360823.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>400565.94</t>
+          <t>393916.32</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-105265</t>
+          <t>-92328</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1486.925046397366</t>
+          <t>-8561.997267127586</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-35773.44</v>
+        <v>-47474.89</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4844.0</t>
+          <t>5294.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.14</t>
+          <t>-27.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-30.56</t>
+          <t>-48.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-65.90</t>
+          <t>-69.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>377379.9841040462</t>
+          <t>377876.9350649351</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>179768.0</t>
+          <t>191748.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>325526.4</t>
+          <t>281278.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>412786.5</t>
+          <t>386543.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>400741.28</t>
+          <t>400565.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-87260</t>
+          <t>-105265</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4746.986999508627</t>
+          <t>-1486.925046397366</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-24548.74</v>
+        <v>-35773.44</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,37 +5770,37 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>230.98</t>
+          <t>229.28</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>230.29</t>
+          <t>230.34</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>430123.4</t>
+          <t>451284.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1191948.4</t>
+          <t>1190565.96</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-58802.8</v>
+        <v>-52095.5</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5998,27 +5998,27 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>232.15</t>
+          <t>230.98</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>229.96</t>
+          <t>230.29</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>435737.0</t>
+          <t>430123.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1189336.42</t>
+          <t>1191948.4</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-61040.47</v>
+        <v>-58802.8</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6429,27 +6429,27 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>233.28</t>
+          <t>232.15</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>229.57</t>
+          <t>229.96</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>379052.8</t>
+          <t>435737.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1181965.28</t>
+          <t>1189336.42</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-91884.92999999999</v>
+        <v>-61040.47</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6860,27 +6860,27 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>2120.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>225.1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>233.52</t>
+          <t>233.28</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>229.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>217.69</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>-1010.12</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-101.04</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>340930.8</t>
+          <t>379052.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>373683.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1178670.4</t>
+          <t>1181965.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>-133148.7005222207</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-111817.38</v>
+        <v>-91884.92999999999</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7291,27 +7291,27 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1462.0</t>
+          <t>1283.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>228.4</t>
+          <t>226.8</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>233.78</t>
+          <t>233.52</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>228.51</t>
+          <t>229.07</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.32</t>
+          <t>217.53</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-259.94</t>
+          <t>-658.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-98.41</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>332244.0</t>
+          <t>288867.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>354728.8</t>
+          <t>340930.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>417109.1</t>
+          <t>402140.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1178768.08</t>
+          <t>1178670.4</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-62380</t>
+          <t>-61209</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-145893.7178646864</t>
+          <t>-140651.2043681088</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-116580.69</v>
+        <v>-111817.38</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7722,27 +7722,27 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1854.0</t>
+          <t>1462.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>228.4</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>234.52</t>
+          <t>233.78</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>227.97</t>
+          <t>228.51</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.08</t>
+          <t>217.32</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-147.83</t>
+          <t>-259.94</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>417173.0</t>
+          <t>332244.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>366152.8</t>
+          <t>354728.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>437954.8</t>
+          <t>417109.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1179346.74</t>
+          <t>1178768.08</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-71802</t>
+          <t>-62380</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-151223.3594609867</t>
+          <t>-145893.7178646864</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-123869.36</v>
+        <v>-116580.69</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8153,27 +8153,27 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1854.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-22.92</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>230.7</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>235.02</t>
+          <t>234.52</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>227.33</t>
+          <t>227.97</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>216.79</t>
+          <t>217.08</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-112.55</t>
+          <t>-147.83</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-90.52</t>
+          <t>-93.08</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>384077.0</t>
+          <t>417173.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>350952.6</t>
+          <t>366152.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>455306.6</t>
+          <t>437954.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1181440.22</t>
+          <t>1179346.74</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-104354</t>
+          <t>-71802</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-156196.8146667503</t>
+          <t>-151223.3594609867</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-138957.37</v>
+        <v>-123869.36</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8584,27 +8584,27 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1682.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-22.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>231.9</t>
+          <t>230.7</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>235.82</t>
+          <t>235.02</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>226.62</t>
+          <t>227.33</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>216.79</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-78.04</t>
+          <t>-112.55</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-90.52</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>282293.0</t>
+          <t>384077.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>368314.2</t>
+          <t>350952.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>468032.0</t>
+          <t>455306.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1179822.7</t>
+          <t>1181440.22</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-99717</t>
+          <t>-104354</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-159331.2596895306</t>
+          <t>-156196.8146667503</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-152002.91</v>
+        <v>-138957.37</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9015,27 +9015,27 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>232.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1569.0</t>
+          <t>1212.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>232.1</t>
+          <t>231.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>236.72</t>
+          <t>235.82</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>226.62</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>216.31</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-67.50</t>
+          <t>-78.04</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-87.85</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>357857.0</t>
+          <t>282293.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>463349.8</t>
+          <t>368314.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>497062.0</t>
+          <t>468032.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1178345.28</t>
+          <t>1179822.7</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-33712</t>
+          <t>-99717</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-160663.6876940798</t>
+          <t>-159331.2596895306</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-154305.29</v>
+        <v>-152002.91</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9446,27 +9446,27 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1569.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>233.2</t>
+          <t>232.1</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>237.9</t>
+          <t>236.72</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>225.72</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>216.02</t>
+          <t>216.31</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-63.85</t>
+          <t>-67.50</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-85.48</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>389364.0</t>
+          <t>357857.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>479489.4</t>
+          <t>463349.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>555156.2</t>
+          <t>497062.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1176598.08</t>
+          <t>1178345.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-75666</t>
+          <t>-33712</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-161819.7607951866</t>
+          <t>-160663.6876940798</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-160179.64</v>
+        <v>-154305.29</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9877,27 +9877,27 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>235.5</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1455.0</t>
+          <t>1682.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>234.5</t>
+          <t>233.2</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>238.55</t>
+          <t>237.9</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>223.89</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>215.81</t>
+          <t>216.02</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-50.02</t>
+          <t>-63.85</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-80.32</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>903696.6611271678</t>
+          <t>903340.7857142858</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>341172.0</t>
+          <t>389364.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>509756.8</t>
+          <t>479489.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>562917.4</t>
+          <t>555156.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1180828.9</t>
+          <t>1176598.08</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-53160</t>
+          <t>-75666</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-162117.9646334989</t>
+          <t>-161819.7607951866</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-166226.62</v>
+        <v>-160179.64</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>83.04</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10308,27 +10308,27 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>半導體業右上上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>235.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>231.5</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1299298.4</t>
+          <t>741994.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>545802.54</t>
+          <t>550504.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>87572.06</v>
+        <v>27691.06</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1714683.2</t>
+          <t>1299298.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>538423.64</t>
+          <t>545802.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>157331.23</v>
+        <v>87572.06</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-7.86</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1757941.0</t>
+          <t>1714683.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>520887.4</t>
+          <t>538423.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>194316.58</v>
+        <v>157331.23</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,98 +2281,98 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1700302.2</t>
+          <t>1757941.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>512978.0</t>
+          <t>520887.4</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>284361.66</v>
+        <v>194316.58</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>68184.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1499818.2</t>
+          <t>1700302.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>884156.4</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>505646.14</t>
+          <t>512978.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>615661</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>68932.8917490568</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>333318.44</v>
+        <v>284361.66</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56809.0</t>
+          <t>68184.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,74 +3048,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-11.85</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>69.63</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-3.51</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>52.20</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>38.6</t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2558102.0</t>
+          <t>3149560.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>895619.8</t>
+          <t>1499818.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>588449.0</t>
+          <t>884156.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>445840.3</t>
+          <t>505646.14</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>307170</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20862.79288512989</t>
+          <t>68932.8917490568</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>187880.56</v>
+        <v>333318.44</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29825.0</t>
+          <t>56809.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,22 +3489,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>52.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,33 +3574,33 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>83.32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1229949.0</t>
+          <t>2558102.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>422349.0</t>
+          <t>895619.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>373937.7</t>
+          <t>588449.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>404007.8</t>
+          <t>445840.3</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>307170</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9504.073928487198</t>
+          <t>20862.79288512989</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>36772.65</v>
+        <v>187880.56</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>56.68</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8372.0</t>
+          <t>29825.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-40.33</t>
+          <t>12.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-44.96</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-79.91</t>
+          <t>-78.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>313411.0</t>
+          <t>1229949.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>212312.8</t>
+          <t>422349.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>355794.3</t>
+          <t>373937.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>384646.18</t>
+          <t>404007.8</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-143481</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-17918.02324077976</t>
+          <t>-9504.073928487198</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-38107</v>
+        <v>36772.65</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6784.0</t>
+          <t>8372.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-40.33</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.49</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>56.83</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.56</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>33.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-62.85</t>
+          <t>-44.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-77.65</t>
+          <t>-79.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>248069.0</t>
+          <t>313411.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>204972.0</t>
+          <t>212312.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>365122.0</t>
+          <t>355794.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>387093.56</t>
+          <t>384646.18</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-160150</t>
+          <t>-143481</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-14247.29989475405</t>
+          <t>-17918.02324077976</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-45516.46</v>
+        <v>-38107</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3691.0</t>
+          <t>6784.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.49</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-70.55</t>
+          <t>-62.85</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-74.14</t>
+          <t>-77.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>128568.0</t>
+          <t>248069.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>268494.6</t>
+          <t>204972.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>360823.1</t>
+          <t>365122.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>393916.32</t>
+          <t>387093.56</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-92328</t>
+          <t>-160150</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8561.997267127586</t>
+          <t>-14247.29989475405</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-47474.89</v>
+        <v>-45516.46</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5294.0</t>
+          <t>3691.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>36.37</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-48.39</t>
+          <t>-70.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-69.58</t>
+          <t>-74.14</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>377876.9350649351</t>
+          <t>378117.1145533142</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>191748.0</t>
+          <t>128568.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>281278.2</t>
+          <t>268494.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>386543.3</t>
+          <t>360823.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>400565.94</t>
+          <t>393916.32</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-105265</t>
+          <t>-92328</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1486.925046397366</t>
+          <t>-8561.997267127586</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-35773.44</v>
+        <v>-47474.89</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>229.28</t>
+          <t>227.1</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>230.34</t>
+          <t>230.35</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>451284.6</t>
+          <t>458840.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1190565.96</t>
+          <t>1187183.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-52095.5</v>
+        <v>-54453.14</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5943,17 +5943,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,37 +6201,37 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>230.98</t>
+          <t>229.28</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>230.29</t>
+          <t>230.34</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>430123.4</t>
+          <t>451284.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1191948.4</t>
+          <t>1190565.96</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-58802.8</v>
+        <v>-52095.5</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>232.15</t>
+          <t>230.98</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>229.96</t>
+          <t>230.29</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>435737.0</t>
+          <t>430123.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1189336.42</t>
+          <t>1191948.4</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-61040.47</v>
+        <v>-58802.8</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>233.28</t>
+          <t>232.15</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>229.57</t>
+          <t>229.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>379052.8</t>
+          <t>435737.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1181965.28</t>
+          <t>1189336.42</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-91884.92999999999</v>
+        <v>-61040.47</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>2120.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>225.1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>233.52</t>
+          <t>233.28</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>229.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>217.69</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>-1010.12</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-101.04</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>340930.8</t>
+          <t>379052.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>373683.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1178670.4</t>
+          <t>1181965.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>-133148.7005222207</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-111817.38</v>
+        <v>-91884.92999999999</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1462.0</t>
+          <t>1283.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-12.78</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>228.4</t>
+          <t>226.8</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>233.78</t>
+          <t>233.52</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>228.51</t>
+          <t>229.07</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.32</t>
+          <t>217.53</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-259.94</t>
+          <t>-658.29</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-98.41</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>332244.0</t>
+          <t>288867.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>354728.8</t>
+          <t>340930.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>417109.1</t>
+          <t>402140.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1178768.08</t>
+          <t>1178670.4</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-62380</t>
+          <t>-61209</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-145893.7178646864</t>
+          <t>-140651.2043681088</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-116580.69</v>
+        <v>-111817.38</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1854.0</t>
+          <t>1462.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-12.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>228.4</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>234.52</t>
+          <t>233.78</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>227.97</t>
+          <t>228.51</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.08</t>
+          <t>217.32</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-147.83</t>
+          <t>-259.94</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>417173.0</t>
+          <t>332244.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>366152.8</t>
+          <t>354728.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>437954.8</t>
+          <t>417109.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1179346.74</t>
+          <t>1178768.08</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-71802</t>
+          <t>-62380</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-151223.3594609867</t>
+          <t>-145893.7178646864</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-123869.36</v>
+        <v>-116580.69</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1854.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-22.92</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>230.7</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>235.02</t>
+          <t>234.52</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>227.33</t>
+          <t>227.97</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>216.79</t>
+          <t>217.08</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-112.55</t>
+          <t>-147.83</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-90.52</t>
+          <t>-93.08</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>384077.0</t>
+          <t>417173.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>350952.6</t>
+          <t>366152.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>455306.6</t>
+          <t>437954.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1181440.22</t>
+          <t>1179346.74</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-104354</t>
+          <t>-71802</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-156196.8146667503</t>
+          <t>-151223.3594609867</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-138957.37</v>
+        <v>-123869.36</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1682.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-13.28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-22.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>231.9</t>
+          <t>230.7</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>235.82</t>
+          <t>235.02</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>226.62</t>
+          <t>227.33</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>216.79</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-78.04</t>
+          <t>-112.55</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-90.52</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>282293.0</t>
+          <t>384077.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>368314.2</t>
+          <t>350952.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>468032.0</t>
+          <t>455306.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1179822.7</t>
+          <t>1181440.22</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-99717</t>
+          <t>-104354</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-159331.2596895306</t>
+          <t>-156196.8146667503</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-152002.91</v>
+        <v>-138957.37</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>232.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1569.0</t>
+          <t>1212.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-15.79</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>232.1</t>
+          <t>231.9</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>236.72</t>
+          <t>235.82</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>226.62</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>216.31</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-67.50</t>
+          <t>-78.04</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-87.85</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>357857.0</t>
+          <t>282293.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>463349.8</t>
+          <t>368314.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>497062.0</t>
+          <t>468032.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1178345.28</t>
+          <t>1179822.7</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-33712</t>
+          <t>-99717</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-160663.6876940798</t>
+          <t>-159331.2596895306</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-154305.29</v>
+        <v>-152002.91</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1569.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>-16.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>233.2</t>
+          <t>232.1</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>237.9</t>
+          <t>236.72</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>225.72</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>216.02</t>
+          <t>216.31</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-63.85</t>
+          <t>-67.50</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-85.48</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>903340.7857142858</t>
+          <t>902745.1534582132</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>389364.0</t>
+          <t>357857.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>479489.4</t>
+          <t>463349.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>555156.2</t>
+          <t>497062.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1176598.08</t>
+          <t>1178345.28</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-75666</t>
+          <t>-33712</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-161819.7607951866</t>
+          <t>-160663.6876940798</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-160179.64</v>
+        <v>-154305.29</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>83.04</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>235.5</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>741994.6</t>
+          <t>584805.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>550504.28</t>
+          <t>554651.52</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>27691.06</v>
+        <v>-7305.19</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1299298.4</t>
+          <t>741994.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>545802.54</t>
+          <t>550504.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>87572.06</v>
+        <v>27691.06</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1714683.2</t>
+          <t>1299298.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>538423.64</t>
+          <t>545802.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>157331.23</v>
+        <v>87572.06</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1757941.0</t>
+          <t>1714683.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>520887.4</t>
+          <t>538423.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>194316.58</v>
+        <v>157331.23</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,22 +2712,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1700302.2</t>
+          <t>1757941.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>512978.0</t>
+          <t>520887.4</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>284361.66</v>
+        <v>194316.58</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>68184.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1499818.2</t>
+          <t>1700302.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>884156.4</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>505646.14</t>
+          <t>512978.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>615661</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>68932.8917490568</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>333318.44</v>
+        <v>284361.66</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56809.0</t>
+          <t>68184.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,74 +3479,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>69.63</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-7.39</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>52.20</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>38.6</t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2558102.0</t>
+          <t>3149560.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>895619.8</t>
+          <t>1499818.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>588449.0</t>
+          <t>884156.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>445840.3</t>
+          <t>505646.14</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>307170</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20862.79288512989</t>
+          <t>68932.8917490568</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>187880.56</v>
+        <v>333318.44</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29825.0</t>
+          <t>56809.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,22 +3920,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>52.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4005,22 +4005,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>83.32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1229949.0</t>
+          <t>2558102.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>422349.0</t>
+          <t>895619.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>373937.7</t>
+          <t>588449.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>404007.8</t>
+          <t>445840.3</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>307170</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9504.073928487198</t>
+          <t>20862.79288512989</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>36772.65</v>
+        <v>187880.56</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>56.68</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8372.0</t>
+          <t>29825.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-40.33</t>
+          <t>12.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-44.96</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-79.91</t>
+          <t>-78.83</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>313411.0</t>
+          <t>1229949.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>212312.8</t>
+          <t>422349.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>355794.3</t>
+          <t>373937.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>384646.18</t>
+          <t>404007.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-143481</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-17918.02324077976</t>
+          <t>-9504.073928487198</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-38107</v>
+        <v>36772.65</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6784.0</t>
+          <t>8372.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-40.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>70.49</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>56.83</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.56</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>33.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-62.85</t>
+          <t>-44.96</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.65</t>
+          <t>-79.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>248069.0</t>
+          <t>313411.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>204972.0</t>
+          <t>212312.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>365122.0</t>
+          <t>355794.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>387093.56</t>
+          <t>384646.18</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-160150</t>
+          <t>-143481</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-14247.29989475405</t>
+          <t>-17918.02324077976</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-45516.46</v>
+        <v>-38107</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3691.0</t>
+          <t>6784.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.49</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-70.55</t>
+          <t>-62.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.14</t>
+          <t>-77.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378117.1145533142</t>
+          <t>378575.6741007195</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>128568.0</t>
+          <t>248069.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>268494.6</t>
+          <t>204972.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>360823.1</t>
+          <t>365122.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>393916.32</t>
+          <t>387093.56</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-92328</t>
+          <t>-160150</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8561.997267127586</t>
+          <t>-14247.29989475405</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-47474.89</v>
+        <v>-45516.46</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>227.1</t>
+          <t>225.2</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>230.35</t>
+          <t>230.45</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>458840.8</t>
+          <t>419383.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1187183.2</t>
+          <t>1181679.14</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-54453.14</v>
+        <v>-58569.72</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5998,27 +5998,27 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>229.28</t>
+          <t>227.1</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>230.34</t>
+          <t>230.35</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>451284.6</t>
+          <t>458840.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1190565.96</t>
+          <t>1187183.2</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-52095.5</v>
+        <v>-54453.14</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6429,27 +6429,27 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,37 +6632,37 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>230.98</t>
+          <t>229.28</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>230.29</t>
+          <t>230.34</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>430123.4</t>
+          <t>451284.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1191948.4</t>
+          <t>1190565.96</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-58802.8</v>
+        <v>-52095.5</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6860,27 +6860,27 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>232.15</t>
+          <t>230.98</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>229.96</t>
+          <t>230.29</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>435737.0</t>
+          <t>430123.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1189336.42</t>
+          <t>1191948.4</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-61040.47</v>
+        <v>-58802.8</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7291,27 +7291,27 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>233.28</t>
+          <t>232.15</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>229.57</t>
+          <t>229.96</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>379052.8</t>
+          <t>435737.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1181965.28</t>
+          <t>1189336.42</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-91884.92999999999</v>
+        <v>-61040.47</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7722,27 +7722,27 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>2120.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-12.78</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>225.1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>233.52</t>
+          <t>233.28</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>229.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>217.69</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>-1010.12</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-101.04</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>340930.8</t>
+          <t>379052.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>373683.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1178670.4</t>
+          <t>1181965.28</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>-133148.7005222207</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-111817.38</v>
+        <v>-91884.92999999999</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8153,27 +8153,27 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1462.0</t>
+          <t>1283.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.28</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>228.4</t>
+          <t>226.8</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>233.78</t>
+          <t>233.52</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>228.51</t>
+          <t>229.07</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.32</t>
+          <t>217.53</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-259.94</t>
+          <t>-658.29</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-98.41</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>332244.0</t>
+          <t>288867.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>354728.8</t>
+          <t>340930.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>417109.1</t>
+          <t>402140.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1178768.08</t>
+          <t>1178670.4</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-62380</t>
+          <t>-61209</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-145893.7178646864</t>
+          <t>-140651.2043681088</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-116580.69</v>
+        <v>-111817.38</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8584,27 +8584,27 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1854.0</t>
+          <t>1462.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>228.4</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>234.52</t>
+          <t>233.78</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>227.97</t>
+          <t>228.51</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>217.08</t>
+          <t>217.32</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-147.83</t>
+          <t>-259.94</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>417173.0</t>
+          <t>332244.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>366152.8</t>
+          <t>354728.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>437954.8</t>
+          <t>417109.1</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1179346.74</t>
+          <t>1178768.08</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-71802</t>
+          <t>-62380</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-151223.3594609867</t>
+          <t>-145893.7178646864</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-123869.36</v>
+        <v>-116580.69</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9015,27 +9015,27 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1854.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.28</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-22.92</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,212 +9198,212 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>229.5</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>234.52</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>227.97</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>217.08</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-147.83</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-93.08</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>902041.0899280576</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>417173.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>366152.8</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>437954.8</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>1179346.74</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-71802</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-151223.3594609867</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-123869.36</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>230.7</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>235.02</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>227.33</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>216.79</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-112.55</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>17.97</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-90.52</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/08/26</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>902745.1534582132</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>384077.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>350952.6</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>455306.6</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1181440.22</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-104354</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-156196.8146667503</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-138957.37</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>224.0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>原相</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>原相</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>-2.745441860838094</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-2.833748607962057</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>11.16140863420413</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
       <c r="BT21" t="inlineStr">
         <is>
           <t>14.75</t>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9446,27 +9446,27 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1682.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-15.79</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-22.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>231.9</t>
+          <t>230.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>235.82</t>
+          <t>235.02</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>226.62</t>
+          <t>227.33</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>216.79</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-78.04</t>
+          <t>-112.55</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-90.52</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>282293.0</t>
+          <t>384077.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>368314.2</t>
+          <t>350952.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>468032.0</t>
+          <t>455306.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1179822.7</t>
+          <t>1181440.22</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-99717</t>
+          <t>-104354</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-159331.2596895306</t>
+          <t>-156196.8146667503</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-152002.91</v>
+        <v>-138957.37</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9877,27 +9877,27 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>232.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1569.0</t>
+          <t>1212.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.79</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-21.31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>232.1</t>
+          <t>231.9</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>236.72</t>
+          <t>235.82</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>226.62</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>216.31</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-67.50</t>
+          <t>-78.04</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-87.85</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>902745.1534582132</t>
+          <t>902041.0899280576</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>357857.0</t>
+          <t>282293.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>463349.8</t>
+          <t>368314.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>497062.0</t>
+          <t>468032.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1178345.28</t>
+          <t>1179822.7</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-33712</t>
+          <t>-99717</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-160663.6876940798</t>
+          <t>-159331.2596895306</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-154305.29</v>
+        <v>-152002.91</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>84.61</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10308,27 +10308,27 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ13"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5560.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-62.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,37 +928,37 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -983,43 +983,43 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,121 +1029,121 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>392234.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>552802.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>219162</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1152,17 +1152,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>半導體業右下上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,87 +1344,87 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,150 +1465,150 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>223.02</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>230.31</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>351582.6</t>
+          <t>551133.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1170503.62</t>
+          <t>552940.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>328496</v>
+        <v>433245</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -1623,82 +1623,82 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1708,32 +1708,32 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1750,17 +1750,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,87 +1780,87 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,165 +1886,165 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>225.2</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>230.45</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>419383.0</t>
+          <t>584805.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1181679.14</t>
+          <t>554651.52</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>275614</v>
+        <v>464544</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -2059,82 +2059,82 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2144,32 +2144,32 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2186,17 +2186,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,87 +2216,87 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-8.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,165 +2322,165 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>227.1</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>230.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>458840.8</t>
+          <t>741994.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1187183.2</t>
+          <t>550504.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>326648</v>
+        <v>363041</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -2495,82 +2495,82 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,87 +2652,87 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,165 +2758,165 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>229.28</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>230.34</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>451284.6</t>
+          <t>1299298.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1190565.96</t>
+          <t>545802.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-52095.49631496938</t>
+          <t>87572.0578340583</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>438050</v>
+        <v>481178</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -2931,82 +2931,82 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,87 +3088,87 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,165 +3194,165 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>230.98</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>230.29</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>430123.4</t>
+          <t>1714683.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1191948.4</t>
+          <t>538423.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-58802.80431880965</t>
+          <t>157331.2318697403</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>389105</v>
+        <v>1013660</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -3367,82 +3367,82 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3452,32 +3452,32 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3494,17 +3494,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,87 +3524,87 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,165 +3630,165 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>232.15</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>229.96</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>435737.0</t>
+          <t>1757941.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1189336.42</t>
+          <t>520887.4</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-61040.46559862403</t>
+          <t>194316.5793539381</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>667498</v>
+        <v>601605</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -3803,82 +3803,82 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,87 +3960,87 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-16.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4050,181 +4050,181 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>233.28</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>229.57</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>379052.8</t>
+          <t>1700302.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1181965.28</t>
+          <t>512978.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-91884.92936983652</t>
+          <t>284361.66221158</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>472903</v>
+        <v>1250489</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -4239,82 +4239,82 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4324,32 +4324,32 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>68184.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,87 +4396,87 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-13.64</t>
+          <t>-21.71</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>69.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -4486,181 +4486,181 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>233.52</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>3149560.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>340930.8</t>
+          <t>1499818.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>884156.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1178670.4</t>
+          <t>505646.14</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>68932.8917490568</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-111817.3801369317</t>
+          <t>333318.4355006547</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>288867</v>
+        <v>3149560</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
@@ -4675,82 +4675,82 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4760,32 +4760,32 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -4802,17 +4802,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1462.0</t>
+          <t>56809.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,87 +4832,87 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-16.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>52.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -4922,181 +4922,181 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>83.32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>228.4</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>233.78</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>228.51</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>217.32</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-259.94</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>332244.0</t>
+          <t>2558102.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>354728.8</t>
+          <t>895619.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>417109.1</t>
+          <t>588449.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1178768.08</t>
+          <t>445840.3</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-62380</t>
+          <t>307170</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-145893.7178646864</t>
+          <t>20862.79288512989</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-116580.6890850344</t>
+          <t>187880.5603600239</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>332244</v>
+        <v>2558102</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>56.68</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -5111,82 +5111,82 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5196,32 +5196,32 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5238,17 +5238,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1854.0</t>
+          <t>29825.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>12.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,37 +5288,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,136 +5374,136 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>234.52</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>227.97</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>217.08</t>
+          <t>33.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-147.83</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>-78.83</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>378893.406025825</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>417173.0</t>
+          <t>1229949.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>366152.8</t>
+          <t>422349.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>437954.8</t>
+          <t>373937.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1179346.74</t>
+          <t>404007.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-71802</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-151223.3594609867</t>
+          <t>-9504.073928487198</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-123869.355829287</t>
+          <t>36772.64728912187</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>417173</v>
+        <v>1229949</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5512,27 +5512,27 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -5547,27 +5547,27 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2.745441860838094</t>
+          <t>16.66616779909605</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2.833748607962057</t>
+          <t>112.5660684339452</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>11.16140863420413</t>
+          <t>-3.455408850505412</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,52 +5577,52 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>59.29%</t>
+          <t>12.66%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+          <t>記憶體及類比邏輯系統Ics99.99%、其他0.01% (2024年)</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>原相-半導體業-上櫃</t>
+          <t>鈺創-半導體業-上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5632,32 +5632,32 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>77.48</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+          <t>** 人工智慧 - 系統整合、領域解決方案、電腦視覺** 體驗科技 - 處理器/IC、感測器/模組、頭顯裝置品牌廠、CPU、GPU、HPU、SoC、IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、語音、手勢/動作、觸覺、VR Headset、AR Smart Glasses、MR Headset &amp; SG** 半導體 - 記憶體IC</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1682.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5704,17 +5704,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-22.92</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,62 +5825,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>230.7</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>235.02</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>227.33</t>
+          <t>229.9</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>216.79</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-112.55</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-90.52</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>901453.0193965518</t>
+          <t>900733.9347202296</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>384077.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>350952.6</t>
+          <t>327128.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>455306.6</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1181440.22</t>
+          <t>1132112.48</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-104354</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-156196.8146667503</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-138957.367041459</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>384077</v>
+        <v>266834</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6068,35 +6068,4395 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>202.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>202.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>196.5</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-3.98</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1651.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-10.69</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-16.81</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9.61</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-2.70</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-8.75</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-3.16</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>223.02</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>230.31</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>217.82</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-68.34</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-8.13</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-4.83</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-126.89</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>328496.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>351582.6</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>393659.8</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>1170503.62</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-42077</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-84676.36423616367</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-56020.92669104022</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>328496</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-11.61</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>201.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>196.5</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1341.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>206.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-4.04</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-13.45</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7.81</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>22.81</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-8.30</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>206.5</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>225.2</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>230.45</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>217.88</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-81.07</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-7.25</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-4.01</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-122.30</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>275614.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>419383.0</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>399217.9</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>1181679.14</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>20165</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-89886.44378982249</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-58569.71761440305</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>275614</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-8.04</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>204.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>203.0</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>206.0</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1622.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14.74</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-16.18</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>-3.01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-4.91</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-7.62</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>209.8</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>227.1</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>230.35</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>217.84</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-114.15</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-6.84</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-117.78</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>326648.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>458840.8</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>399885.8</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>1187183.2</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>58955</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-95580.3940035351</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-54453.1433044069</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>326648</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>-10.94</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>202.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>205.5</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-3.81</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2122.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>203.0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>11.98</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-14.71</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-3.69</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-5.54</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-6.27</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>229.28</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>230.34</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>217.91</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-143.19</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-5.55</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-112.70</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>438050.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>451284.6</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>403006.7</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>1190565.96</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>48277</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-103058.0759488311</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-52095.49631496938</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>438050</v>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>-9.38</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>210.5</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>203.0</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>203.0</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1833.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-6.57</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-11.34</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10.67</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-5.14</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>5.68</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>219.1</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>230.98</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>230.29</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>217.91</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-185.29</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-4.18</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-108.16</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>389105.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>430123.4</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>398138.1</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>1191948.4</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>31985</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-112323.9995186242</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-58802.80431880965</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>389105</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>-5.80</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>214.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>210.5</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-4.36</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3066.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>213.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-7.58</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>10.78</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-10.50</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17.85</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-4.93</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-4.27</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-4.16</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>222.5</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>232.15</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>229.96</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>217.77</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-305.02</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-104.38</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>667498.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>435737.0</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>393344.8</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>1189336.42</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>42392</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-122055.1259185904</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-61040.46559862403</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>667498</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>-4.91</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>218.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>223.5</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>213.0</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>213.0</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2120.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>222.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-12.37</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-6.51</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12.34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-3.50</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>5.46</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>225.1</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>233.28</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>229.57</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>217.69</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-1010.12</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-101.04</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>472903.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>379052.8</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>373683.5</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>1181965.28</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>5369</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-133148.7005222207</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-91884.92936983652</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>472903</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>221.5</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>222.5</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1283.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>225.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-13.64</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-15.22</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-5.46</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-2.88</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>226.8</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>233.52</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>229.07</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>217.53</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-658.29</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-98.41</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>288867.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>340930.8</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>402140.3</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>1178670.4</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-61209</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-140651.2043681088</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-111817.3801369317</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>288867</v>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>225.5</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>223.0</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>225.0</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1462.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-13.13</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-14.96</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-5.88</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>8.51</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-1.93</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>228.4</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>233.78</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>228.51</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>217.32</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-259.94</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-95.80</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>332244.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>354728.8</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>417109.1</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>1178768.08</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-62380</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-145893.7178646864</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-116580.6890850344</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>332244</v>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>230.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>77.48</t>
+        </is>
+      </c>
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1854.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-15.15</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-16.39</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10.79</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>10.89</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
           <t>229.5</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>232.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>234.52</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>227.97</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>217.08</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-147.83</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-93.08</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/08/26</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>900733.9347202296</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>417173.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>366152.8</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>437954.8</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>1179346.74</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-71802</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-151223.3594609867</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-123869.355829287</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>417173</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-2.745441860838094</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>-2.833748607962057</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>11.16140863420413</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>17.27%</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>82.03</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>29690</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>CMOS影像感測元件97.67%、其他2.33% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>原相-半導體業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>半導體業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
         <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>230.0</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>220.5</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
         <is>
           <t>77.48</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 觸控面板 - 控制IC** 汽車 - 其他** 人工智慧 - 機器學習、電腦視覺、移動控制** 運動科技 - 感測裝置** 半導體 - 影像感測IC** 太空衛星科技 - 感測器** 體驗科技 - IC、環境感知、深度感測、SLAM、其他、使用者感知、視覺、手勢/動作、觸覺</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-62.77</t>
+          <t>-58.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-27.71</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>219162.0</t>
+          <t>203433.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>392234.0</t>
+          <t>336685.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1053458.6</t>
+          <t>817991.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>552802.24</t>
+          <t>553429.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-661224</t>
+          <t>-481306</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>46996.04209503077</t>
+          <t>25761.10630086278</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-67837.9214130668</t>
+          <t>-91031.04056706117</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>219162</v>
+        <v>203433</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10767.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,72 +1334,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-62.77</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-52.26</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>551133.6</t>
+          <t>392234.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1154537.3</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>552940.56</t>
+          <t>552802.24</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-603403</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>67874.94455104851</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-33967.36114260822</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>433245</v>
+        <v>219162</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10659.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>584805.6</t>
+          <t>551133.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1142553.9</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>554651.52</t>
+          <t>552940.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-557748</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>86391.72740444065</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-7305.190715431352</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>464544</v>
+        <v>433245</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.81</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>741994.6</t>
+          <t>584805.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>550504.28</t>
+          <t>554651.52</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>27691.05956322944</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>363041</v>
+        <v>464544</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1299298.4</t>
+          <t>741994.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>545802.54</t>
+          <t>550504.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87572.0578340583</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>481178</v>
+        <v>363041</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1714683.2</t>
+          <t>1299298.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>538423.64</t>
+          <t>545802.54</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>157331.2318697403</t>
+          <t>87572.0578340583</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1013660</v>
+        <v>481178</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1757941.0</t>
+          <t>1714683.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>520887.4</t>
+          <t>538423.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>194316.5793539381</t>
+          <t>157331.2318697403</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>601605</v>
+        <v>1013660</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-16.6</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,98 +4045,98 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1700302.2</t>
+          <t>1757941.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>512978.0</t>
+          <t>520887.4</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>284361.66221158</t>
+          <t>194316.5793539381</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1250489</v>
+        <v>601605</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>68184.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-21.71</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1499818.2</t>
+          <t>1700302.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>884156.4</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>505646.14</t>
+          <t>512978.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>615661</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>68932.8917490568</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>333318.4355006547</t>
+          <t>284361.66221158</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>3149560</v>
+        <v>1250489</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56809.0</t>
+          <t>68184.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,74 +4822,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-20.63</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>69.63</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-16.86</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>52.20</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>39.7</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>38.6</t>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2558102.0</t>
+          <t>3149560.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>895619.8</t>
+          <t>1499818.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>588449.0</t>
+          <t>884156.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>445840.3</t>
+          <t>505646.14</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>307170</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20862.79288512989</t>
+          <t>68932.8917490568</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>187880.5603600239</t>
+          <t>333318.4355006547</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2558102</v>
+        <v>3149560</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29825.0</t>
+          <t>56809.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,22 +5268,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>52.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,33 +5353,33 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>83.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,50 +5464,50 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378893.406025825</t>
+          <t>378787.755730659</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1229949.0</t>
+          <t>2558102.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>422349.0</t>
+          <t>895619.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>373937.7</t>
+          <t>588449.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>404007.8</t>
+          <t>445840.3</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>307170</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-9504.073928487198</t>
+          <t>20862.79288512989</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>36772.64728912187</t>
+          <t>187880.5603600239</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1229949</v>
+        <v>2558102</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>56.68</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>927.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>204.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1345.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>198.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-23.89</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.10</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>200.9</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>219.42</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>229.9</t>
+          <t>229.64</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-55.58</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-131.23</t>
+          <t>-134.54</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>327128.4</t>
+          <t>277235.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>378625.9</t>
+          <t>364259.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1132112.48</t>
+          <t>1109012.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-51497</t>
+          <t>-87024</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-80489.36971943239</t>
+          <t>-77783.48339504802</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-57460.89987741027</t>
+          <t>-62901.108610934</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>266834</v>
+        <v>188584</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
@@ -6073,17 +6073,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>223.02</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>230.31</t>
+          <t>229.9</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>351582.6</t>
+          <t>327128.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1170503.62</t>
+          <t>1132112.48</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>328496</v>
+        <v>266834</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6499,17 +6499,17 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6551,42 +6551,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>-3.98</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1651.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>3.18</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1341.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>206.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-4.04</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>225.2</t>
+          <t>223.02</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>230.45</t>
+          <t>230.31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-126.89</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>419383.0</t>
+          <t>351582.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>393659.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1181679.14</t>
+          <t>1170503.62</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-42077</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>-84676.36423616367</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-56020.92669104022</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>275614</v>
+        <v>328496</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6935,27 +6935,27 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>227.1</t>
+          <t>225.2</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>230.35</t>
+          <t>230.45</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>458840.8</t>
+          <t>419383.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1187183.2</t>
+          <t>1181679.14</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>-58569.71761440305</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>326648</v>
+        <v>275614</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7371,27 +7371,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>229.28</t>
+          <t>227.1</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>230.34</t>
+          <t>230.35</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>451284.6</t>
+          <t>458840.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1190565.96</t>
+          <t>1187183.2</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-52095.49631496938</t>
+          <t>-54453.1433044069</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>438050</v>
+        <v>326648</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7752,17 +7752,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7807,27 +7807,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,37 +8010,37 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>230.98</t>
+          <t>229.28</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>230.29</t>
+          <t>230.34</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>430123.4</t>
+          <t>451284.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1191948.4</t>
+          <t>1190565.96</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-58802.80431880965</t>
+          <t>-52095.49631496938</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>389105</v>
+        <v>438050</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8243,27 +8243,27 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>232.15</t>
+          <t>230.98</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>229.96</t>
+          <t>230.29</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>435737.0</t>
+          <t>430123.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1189336.42</t>
+          <t>1191948.4</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-61040.46559862403</t>
+          <t>-58802.80431880965</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>667498</v>
+        <v>389105</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8679,27 +8679,27 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>233.28</t>
+          <t>232.15</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>229.57</t>
+          <t>229.96</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>379052.8</t>
+          <t>435737.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1181965.28</t>
+          <t>1189336.42</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-91884.92936983652</t>
+          <t>-61040.46559862403</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>472903</v>
+        <v>667498</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9115,27 +9115,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>2120.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.64</t>
+          <t>-8.8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>225.1</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>233.52</t>
+          <t>233.28</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>229.57</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>217.69</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>-1010.12</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-101.04</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>340930.8</t>
+          <t>379052.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>373683.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1178670.4</t>
+          <t>1181965.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>-133148.7005222207</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-111817.3801369317</t>
+          <t>-91884.92936983652</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>288867</v>
+        <v>472903</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9551,27 +9551,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1462.0</t>
+          <t>1283.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>228.4</t>
+          <t>226.8</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>233.78</t>
+          <t>233.52</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>228.51</t>
+          <t>229.07</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>217.32</t>
+          <t>217.53</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-259.94</t>
+          <t>-658.29</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-98.41</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>332244.0</t>
+          <t>288867.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>354728.8</t>
+          <t>340930.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>417109.1</t>
+          <t>402140.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1178768.08</t>
+          <t>1178670.4</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-62380</t>
+          <t>-61209</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-145893.7178646864</t>
+          <t>-140651.2043681088</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-116580.6890850344</t>
+          <t>-111817.3801369317</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>332244</v>
+        <v>288867</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9987,27 +9987,27 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1854.0</t>
+          <t>1462.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>927</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>228.4</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>234.52</t>
+          <t>233.78</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>227.97</t>
+          <t>228.51</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>217.08</t>
+          <t>217.32</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-147.83</t>
+          <t>-259.94</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>900733.9347202296</t>
+          <t>899848.7514326647</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>417173.0</t>
+          <t>332244.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>366152.8</t>
+          <t>354728.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>437954.8</t>
+          <t>417109.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1179346.74</t>
+          <t>1178768.08</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-71802</t>
+          <t>-62380</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-151223.3594609867</t>
+          <t>-145893.7178646864</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-123869.355829287</t>
+          <t>-116580.6890850344</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>417173</v>
+        <v>332244</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10423,27 +10423,27 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右上上櫃</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5060.0</t>
+          <t>5712.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-58.84</t>
+          <t>-41.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-33.79</t>
+          <t>-48.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-40.61</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>336685.0</t>
+          <t>308262.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>817991.7</t>
+          <t>525128.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>553429.18</t>
+          <t>553146.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-481306</t>
+          <t>-216866</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>25761.10630086278</t>
+          <t>5847.359491394556</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-91031.04056706117</t>
+          <t>-103678.2479606807</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>203433</v>
+        <v>220929</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-62.77</t>
+          <t>-58.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-27.71</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>219162.0</t>
+          <t>203433.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>392234.0</t>
+          <t>336685.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1053458.6</t>
+          <t>817991.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>552802.24</t>
+          <t>553429.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-661224</t>
+          <t>-481306</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>46996.04209503077</t>
+          <t>25761.10630086278</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-67837.9214130668</t>
+          <t>-91031.04056706117</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>219162</v>
+        <v>203433</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10767.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,72 +1770,72 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.93</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-62.77</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2.47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-52.26</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,50 +1976,50 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>551133.6</t>
+          <t>392234.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1154537.3</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>552940.56</t>
+          <t>552802.24</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-603403</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>67874.94455104851</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-33967.36114260822</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>433245</v>
+        <v>219162</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10659.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>584805.6</t>
+          <t>551133.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1142553.9</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>554651.52</t>
+          <t>552940.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-557748</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>86391.72740444065</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-7305.190715431352</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>464544</v>
+        <v>433245</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>741994.6</t>
+          <t>584805.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>550504.28</t>
+          <t>554651.52</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>27691.05956322944</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>363041</v>
+        <v>464544</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1299298.4</t>
+          <t>741994.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>545802.54</t>
+          <t>550504.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87572.0578340583</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>481178</v>
+        <v>363041</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1714683.2</t>
+          <t>1299298.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>538423.64</t>
+          <t>545802.54</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>157331.2318697403</t>
+          <t>87572.0578340583</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1013660</v>
+        <v>481178</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-20.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1757941.0</t>
+          <t>1714683.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>520887.4</t>
+          <t>538423.64</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>194316.5793539381</t>
+          <t>157331.2318697403</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>601605</v>
+        <v>1013660</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,98 +4481,98 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1700302.2</t>
+          <t>1757941.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>512978.0</t>
+          <t>520887.4</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>284361.66221158</t>
+          <t>194316.5793539381</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1250489</v>
+        <v>601605</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>68184.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-20.63</t>
+          <t>-19.35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1499818.2</t>
+          <t>1700302.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>884156.4</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>505646.14</t>
+          <t>512978.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>615661</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>68932.8917490568</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>333318.4355006547</t>
+          <t>284361.66221158</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>3149560</v>
+        <v>1250489</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56809.0</t>
+          <t>68184.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,74 +5258,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-24.58</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.93</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>69.63</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-15.82</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.47</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>52.20</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>39.7</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>45.75</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>38.6</t>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378787.755730659</t>
+          <t>378719.9527896995</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2558102.0</t>
+          <t>3149560.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>895619.8</t>
+          <t>1499818.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>588449.0</t>
+          <t>884156.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>445840.3</t>
+          <t>505646.14</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>307170</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20862.79288512989</t>
+          <t>68932.8917490568</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>187880.5603600239</t>
+          <t>333318.4355006547</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2558102</v>
+        <v>3149560</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>927.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-27.43</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>219.42</t>
+          <t>217.92</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>229.64</t>
+          <t>229.57</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>218.03</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-134.54</t>
+          <t>-136.58</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>277235.2</t>
+          <t>261303.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>364259.9</t>
+          <t>360072.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1109012.44</t>
+          <t>1087687.9</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-87024</t>
+          <t>-98768</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-77783.48339504802</t>
+          <t>-75163.91318182944</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-62901.108610934</t>
+          <t>-60756.27700912725</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>188584</v>
+        <v>246990</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1345.0</t>
+          <t>927.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-23.89</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-9.10</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>200.9</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>219.42</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>229.9</t>
+          <t>229.64</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-55.58</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-131.23</t>
+          <t>-134.54</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>327128.4</t>
+          <t>277235.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>378625.9</t>
+          <t>364259.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1132112.48</t>
+          <t>1109012.44</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-51497</t>
+          <t>-87024</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-80489.36971943239</t>
+          <t>-77783.48339504802</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-57460.89987741027</t>
+          <t>-62901.108610934</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>266834</v>
+        <v>188584</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6509,17 +6509,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>223.02</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>230.31</t>
+          <t>229.9</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>351582.6</t>
+          <t>327128.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1170503.62</t>
+          <t>1132112.48</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>328496</v>
+        <v>266834</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1651.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,17 +7118,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>225.2</t>
+          <t>223.02</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>230.45</t>
+          <t>230.31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-126.89</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>419383.0</t>
+          <t>351582.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>393659.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1181679.14</t>
+          <t>1170503.62</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-42077</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>-84676.36423616367</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-56020.92669104022</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>275614</v>
+        <v>328496</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>227.1</t>
+          <t>225.2</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>230.35</t>
+          <t>230.45</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>458840.8</t>
+          <t>419383.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1187183.2</t>
+          <t>1181679.14</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>-58569.71761440305</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>326648</v>
+        <v>275614</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>229.28</t>
+          <t>227.1</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>230.34</t>
+          <t>230.35</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>451284.6</t>
+          <t>458840.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1190565.96</t>
+          <t>1187183.2</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-52095.49631496938</t>
+          <t>-54453.1433044069</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>438050</v>
+        <v>326648</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8188,17 +8188,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,37 +8446,37 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>230.98</t>
+          <t>229.28</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>230.29</t>
+          <t>230.34</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8486,17 +8486,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>430123.4</t>
+          <t>451284.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1191948.4</t>
+          <t>1190565.96</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-58802.80431880965</t>
+          <t>-52095.49631496938</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>389105</v>
+        <v>438050</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>232.15</t>
+          <t>230.98</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>229.96</t>
+          <t>230.29</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>435737.0</t>
+          <t>430123.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1189336.42</t>
+          <t>1191948.4</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-61040.46559862403</t>
+          <t>-58802.80431880965</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>667498</v>
+        <v>389105</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.8</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>233.28</t>
+          <t>232.15</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>229.57</t>
+          <t>229.96</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>379052.8</t>
+          <t>435737.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1181965.28</t>
+          <t>1189336.42</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-91884.92936983652</t>
+          <t>-61040.46559862403</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>472903</v>
+        <v>667498</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>2120.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>225.1</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>233.52</t>
+          <t>233.28</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>229.57</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>217.69</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>-1010.12</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-101.04</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>340930.8</t>
+          <t>379052.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>373683.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1178670.4</t>
+          <t>1181965.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>-133148.7005222207</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-111817.3801369317</t>
+          <t>-91884.92936983652</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>288867</v>
+        <v>472903</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1462.0</t>
+          <t>1283.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-7.91</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>228.4</t>
+          <t>226.8</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>233.78</t>
+          <t>233.52</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>228.51</t>
+          <t>229.07</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>217.32</t>
+          <t>217.53</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-259.94</t>
+          <t>-658.29</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-98.41</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>899848.7514326647</t>
+          <t>899091.4356223176</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>332244.0</t>
+          <t>288867.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>354728.8</t>
+          <t>340930.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>417109.1</t>
+          <t>402140.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1178768.08</t>
+          <t>1178670.4</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-62380</t>
+          <t>-61209</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-145893.7178646864</t>
+          <t>-140651.2043681088</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-116580.6890850344</t>
+          <t>-111817.3801369317</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>332244</v>
+        <v>288867</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>83.99</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>40.06</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>220929.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>308262.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>308262.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>525128.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>553146.32</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>553146.3199999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-103678.2479606807</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>220929</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>220929.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>40.93</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>38.24</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>38.24</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>203433.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>336685.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>336685</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>817991.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>553429.18</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>553429.1800000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-91031.04056706117</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>203433</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>41.87</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>219162.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>392234.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>392234</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1053458.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>552802.24</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>552802.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-67837.9214130668</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>219162</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>219162.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.23</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>40.5</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>433245.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>551133.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>551133.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1154537.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>552940.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>552940.5600000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-33967.36114260822</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>433245</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>433245.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.13</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>40.46</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>37.94</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>37.94</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>464544.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>584805.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>584805.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1142553.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>554651.52</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>554651.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-7305.190715431352</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>464544</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>464544.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>40.19</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>37.75</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>37.75</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>363041.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>741994.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>741994.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1120906.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>550504.28</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>550504.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>27691.05956322944</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>363041</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>363041.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>45.53</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>39.98</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>37.54</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>37.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>481178.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1299298.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1299298.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1097459.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>545802.54</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>545802.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>87572.0578340583</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>481178</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>481178.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>45.84</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1013660.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1714683.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1714683.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1068516.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>538423.64</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>538423.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>157331.2318697403</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1013660</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1013660.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>44.97</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>39.33</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>37.04</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>37.04</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>601605.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1757941.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1757941</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>985126.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>520887.4</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>520887.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>194316.5793539381</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>601605</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>601605.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>43.7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.83</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1250489.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1700302.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1700302.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>952637.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>512978.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>512978</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>284361.66221158</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1250489</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1250489.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>42.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36.6</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3149560.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1499818.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1499818.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>884156.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>505646.14</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>505646.14</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>333318.4355006547</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3149560</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3149560.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>203.0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>217.92</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>246990.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>261303.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>261303.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>360072.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1087687.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1087687.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-60756.27700912725</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>246990</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>246990.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>219.42</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>229.64</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>219.42</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>229.64</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>188584.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>277235.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>277235.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>364259.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1109012.44</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1109012.44</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-62901.108610934</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>188584</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>188584.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>200.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>221.0</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>229.9</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>229.9</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>266834.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>327128.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>327128.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>378625.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1132112.48</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1132112.48</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-57460.89987741027</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>266834</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>266834.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>203.5</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>223.02</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>230.31</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>230.31</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>328496.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>351582.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>351582.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>393659.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1170503.62</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1170503.62</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-56020.92669104022</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>328496</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>328496.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>225.2</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>230.45</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>230.45</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>275614.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>419383.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>419383</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>399217.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1181679.14</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1181679.14</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-58569.71761440305</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>275614</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>275614.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>209.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>227.1</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>230.35</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>230.35</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>326648.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>458840.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>458840.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>399885.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1187183.2</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1187183.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-54453.1433044069</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>326648</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>326648.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>214.9</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>229.28</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>230.34</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>230.34</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>438050.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>451284.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>451284.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>403006.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1190565.96</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1190565.96</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-52095.49631496938</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>438050</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>438050.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>219.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>230.98</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>230.29</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>230.29</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>389105.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>430123.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>430123.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>398138.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1191948.4</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1191948.4</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-58802.80431880965</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>389105</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>389105.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>222.5</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>232.15</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>229.96</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>232.15</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>229.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>667498.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>435737.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>435737</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>393344.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1189336.42</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1189336.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-61040.46559862403</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>667498</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>667498.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>233.28</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>472903.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>379052.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>379052.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>373683.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1181965.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1181965.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-91884.92936983652</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>472903</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>472903.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>226.8</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>233.52</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>229.07</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>229.07</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>288867.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>340930.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>340930.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>402140.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1178670.4</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1178670.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-111817.3801369317</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>288867</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>288867.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5712.0</t>
+          <t>4049.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-41.30</t>
+          <t>-40.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>40.74</v>
+        <v>40.83</v>
       </c>
       <c r="AN2" t="n">
-        <v>38.34</v>
+        <v>38.44</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-48.93</t>
+          <t>-55.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-40.61</t>
+          <t>-47.89</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>308262.6</v>
+        <v>246893.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>525128.6</t>
+          <t>415849.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>553146.3199999999</v>
+        <v>548827.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-216866</t>
+          <t>-168956</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>5847.359491394556</t>
+          <t>-12695.5784206965</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-103678.2479606807</t>
+          <t>-114681.7369371973</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>34.93</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5060.0</t>
+          <t>5712.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-58.84</t>
+          <t>-41.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1444,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>40.69</v>
+        <v>40.74</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.24</v>
+        <v>38.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-33.79</t>
+          <t>-48.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-40.61</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>336685</v>
+        <v>308262.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>817991.7</t>
+          <t>525128.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>553429.1800000001</v>
+        <v>553146.3199999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-481306</t>
+          <t>-216866</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>25761.10630086278</t>
+          <t>5847.359491394556</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-91031.04056706117</t>
+          <t>-103678.2479606807</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-62.77</t>
+          <t>-58.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,176 +1874,176 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>40.56</v>
+        <v>40.69</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.13</v>
+        <v>38.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-33.35</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>378516.8464285714</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>336685</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>817991.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>553429.1800000001</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-481306</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>25761.10630086278</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-91031.04056706117</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>35.27</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-27.71</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>378719.9527896995</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>392234</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>1053458.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>552802.24</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-661224</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>46996.04209503077</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-67837.9214130668</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
       <c r="BN4" t="inlineStr">
         <is>
           <t>16.66616779909605</t>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10767.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,72 +2188,72 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-4.16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-62.77</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-2.93</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-52.26</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>40.5</v>
+        <v>40.56</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.03</v>
+        <v>38.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>551133.6</v>
+        <v>392234</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1154537.3</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>552940.5600000001</v>
+        <v>552802.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-603403</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>67874.94455104851</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-33967.36114260822</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10659.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>40.46</v>
+        <v>40.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.94</v>
+        <v>38.03</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>584805.6</v>
+        <v>551133.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1142553.9</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>554651.52</v>
+        <v>552940.5600000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-557748</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>86391.72740444065</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-7305.190715431352</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>40.19</v>
+        <v>40.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>37.75</v>
+        <v>37.94</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>741994.6</v>
+        <v>584805.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>550504.28</v>
+        <v>554651.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>27691.05956322944</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-8.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>39.98</v>
+        <v>40.19</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.54</v>
+        <v>37.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1299298.4</v>
+        <v>741994.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>545802.54</v>
+        <v>550504.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87572.0578340583</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-20.13</t>
+          <t>-12.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.7</v>
+        <v>39.98</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.31</v>
+        <v>37.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1714683.2</v>
+        <v>1299298.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>538423.64</v>
+        <v>545802.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>157331.2318697403</t>
+          <t>87572.0578340583</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.33</v>
+        <v>39.7</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.04</v>
+        <v>37.31</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1757941</v>
+        <v>1714683.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>520887.4</v>
+        <v>538423.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>194316.5793539381</t>
+          <t>157331.2318697403</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-19.35</t>
+          <t>-12.18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,94 +4863,94 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.02</v>
+        <v>39.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.83</v>
+        <v>37.04</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1700302.2</v>
+        <v>1757941</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>512978</v>
+        <v>520887.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>284361.66221158</t>
+          <t>194316.5793539381</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>68184.0</t>
+          <t>26800.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-24.58</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.19</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.73</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>38.52</v>
+        <v>39.02</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.6</v>
+        <v>36.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-53.19</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378719.9527896995</t>
+          <t>378516.8464285714</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1499818.2</v>
+        <v>1700302.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>884156.4</t>
+          <t>952637.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>505646.14</v>
+        <v>512978</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>615661</t>
+          <t>747665</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>68932.8917490568</t>
+          <t>102075.7795125219</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>333318.4355006547</t>
+          <t>284361.66221158</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3149560.0</t>
+          <t>1250489.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1187.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>57.82</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>203.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>217.92</v>
+        <v>216.72</v>
       </c>
       <c r="AN13" t="n">
-        <v>229.57</v>
+        <v>229.4</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>218.03</t>
+          <t>218.13</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-136.58</t>
+          <t>-137.70</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>261303.6</v>
+        <v>235133.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>360072.2</t>
+          <t>327258.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1087687.9</v>
+        <v>1062345.88</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-98768</t>
+          <t>-92124</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-75163.91318182944</t>
+          <t>-73662.2362250302</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-60756.27700912725</t>
+          <t>-65403.01296263438</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>927.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-27.43</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>219.42</v>
+        <v>217.92</v>
       </c>
       <c r="AN14" t="n">
-        <v>229.64</v>
+        <v>229.57</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>218.03</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-134.54</t>
+          <t>-136.58</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>277235.2</v>
+        <v>261303.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>364259.9</t>
+          <t>360072.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1109012.44</v>
+        <v>1087687.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-87024</t>
+          <t>-98768</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-77783.48339504802</t>
+          <t>-75163.91318182944</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-62901.108610934</t>
+          <t>-60756.27700912725</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1345.0</t>
+          <t>927.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-23.89</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.10</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>200.9</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>221</v>
+        <v>219.42</v>
       </c>
       <c r="AN15" t="n">
-        <v>229.9</v>
+        <v>229.64</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-55.58</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-131.23</t>
+          <t>-134.54</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>327128.4</v>
+        <v>277235.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>378625.9</t>
+          <t>364259.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1132112.48</v>
+        <v>1109012.44</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-51497</t>
+          <t>-87024</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-80489.36971943239</t>
+          <t>-77783.48339504802</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-57460.89987741027</t>
+          <t>-62901.108610934</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>223.02</v>
+        <v>221</v>
       </c>
       <c r="AN16" t="n">
-        <v>230.31</v>
+        <v>229.9</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>351582.6</v>
+        <v>327128.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1170503.62</v>
+        <v>1132112.48</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1651.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>225.2</v>
+        <v>223.02</v>
       </c>
       <c r="AN17" t="n">
-        <v>230.45</v>
+        <v>230.31</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-126.89</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>419383</v>
+        <v>351582.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>393659.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1181679.14</v>
+        <v>1170503.62</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-42077</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>-84676.36423616367</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-56020.92669104022</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>227.1</v>
+        <v>225.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>230.35</v>
+        <v>230.45</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>458840.8</v>
+        <v>419383</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1187183.2</v>
+        <v>1181679.14</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>-58569.71761440305</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>229.28</v>
+        <v>227.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>230.34</v>
+        <v>230.35</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>451284.6</v>
+        <v>458840.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1190565.96</v>
+        <v>1187183.2</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-52095.49631496938</t>
+          <t>-54453.1433044069</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>230.98</v>
+        <v>229.28</v>
       </c>
       <c r="AN20" t="n">
-        <v>230.29</v>
+        <v>230.34</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>430123.4</v>
+        <v>451284.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1191948.4</v>
+        <v>1190565.96</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-58802.80431880965</t>
+          <t>-52095.49631496938</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>232.15</v>
+        <v>230.98</v>
       </c>
       <c r="AN21" t="n">
-        <v>229.96</v>
+        <v>230.29</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>435737</v>
+        <v>430123.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1189336.42</v>
+        <v>1191948.4</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-61040.46559862403</t>
+          <t>-58802.80431880965</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>233.28</v>
+        <v>232.15</v>
       </c>
       <c r="AN22" t="n">
-        <v>229.57</v>
+        <v>229.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>379052.8</v>
+        <v>435737</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1181965.28</v>
+        <v>1189336.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-91884.92936983652</t>
+          <t>-61040.46559862403</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1283.0</t>
+          <t>2120.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>225.1</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>233.52</v>
+        <v>233.28</v>
       </c>
       <c r="AN23" t="n">
-        <v>229.07</v>
+        <v>229.57</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>217.69</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-658.29</t>
+          <t>-1010.12</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-98.41</t>
+          <t>-101.04</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>899091.4356223176</t>
+          <t>898117.2257142856</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>340930.8</v>
+        <v>379052.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>402140.3</t>
+          <t>373683.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1178670.4</v>
+        <v>1181965.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-61209</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-140651.2043681088</t>
+          <t>-133148.7005222207</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-111817.3801369317</t>
+          <t>-91884.92936983652</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>288867.0</t>
+          <t>472903.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4049.0</t>
+          <t>5910.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-40.63</t>
+          <t>-45.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>40.83</v>
+        <v>40.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>38.44</v>
+        <v>38.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-55.91</t>
+          <t>-61.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-47.89</t>
+          <t>-54.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>246893.2</v>
+        <v>207413.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>415849.4</t>
+          <t>379273.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>548827.92</v>
+        <v>543077.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-168956</t>
+          <t>-171860</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12695.5784206965</t>
+          <t>-28227.94494017843</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-114681.7369371973</t>
+          <t>-113655.960797329</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5712.0</t>
+          <t>4049.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-41.30</t>
+          <t>-40.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>40.74</v>
+        <v>40.83</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.34</v>
+        <v>38.44</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-48.93</t>
+          <t>-55.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-40.61</t>
+          <t>-47.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>308262.6</v>
+        <v>246893.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>525128.6</t>
+          <t>415849.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>553146.3199999999</v>
+        <v>548827.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-216866</t>
+          <t>-168956</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5847.359491394556</t>
+          <t>-12695.5784206965</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-103678.2479606807</t>
+          <t>-114681.7369371973</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>34.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5060.0</t>
+          <t>5712.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-58.84</t>
+          <t>-41.30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1874,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>40.69</v>
+        <v>40.74</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.24</v>
+        <v>38.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-33.79</t>
+          <t>-48.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-40.61</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>336685</v>
+        <v>308262.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>817991.7</t>
+          <t>525128.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>553429.1800000001</v>
+        <v>553146.3199999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-481306</t>
+          <t>-216866</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>25761.10630086278</t>
+          <t>5847.359491394556</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-91031.04056706117</t>
+          <t>-103678.2479606807</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-62.77</t>
+          <t>-58.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,176 +2304,176 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>40.56</v>
+        <v>40.69</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.13</v>
+        <v>38.24</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-33.35</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>378481.5427960057</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>336685</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>817991.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>553429.1800000001</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-481306</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>25761.10630086278</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-91031.04056706117</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>35.27</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-27.71</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>378516.8464285714</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>392234</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>1053458.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>552802.24</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-661224</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>46996.04209503077</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-67837.9214130668</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="BN5" t="inlineStr">
         <is>
           <t>16.66616779909605</t>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10767.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,72 +2618,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-3.85</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-62.77</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-4.16</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-52.26</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>40.5</v>
+        <v>40.56</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.03</v>
+        <v>38.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>551133.6</v>
+        <v>392234</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1154537.3</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>552940.5600000001</v>
+        <v>552802.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-603403</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>67874.94455104851</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-33967.36114260822</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10659.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>40.46</v>
+        <v>40.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>37.94</v>
+        <v>38.03</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>584805.6</v>
+        <v>551133.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1142553.9</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>554651.52</v>
+        <v>552940.5600000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-557748</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>86391.72740444065</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7305.190715431352</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.12</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>40.19</v>
+        <v>40.46</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.75</v>
+        <v>37.94</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>741994.6</v>
+        <v>584805.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>550504.28</v>
+        <v>554651.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>27691.05956322944</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.18</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.98</v>
+        <v>40.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.54</v>
+        <v>37.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1299298.4</v>
+        <v>741994.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>545802.54</v>
+        <v>550504.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87572.0578340583</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.7</v>
+        <v>39.98</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.31</v>
+        <v>37.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1714683.2</v>
+        <v>1299298.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>538423.64</v>
+        <v>545802.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>157331.2318697403</t>
+          <t>87572.0578340583</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.18</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.33</v>
+        <v>39.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>37.04</v>
+        <v>37.31</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1757941</v>
+        <v>1714683.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>520887.4</v>
+        <v>538423.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>194316.5793539381</t>
+          <t>157331.2318697403</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26800.0</t>
+          <t>13784.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,94 +5293,94 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>94.73</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.02</v>
+        <v>39.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.83</v>
+        <v>37.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-53.19</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378516.8464285714</t>
+          <t>378481.5427960057</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1700302.2</v>
+        <v>1757941</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>952637.1</t>
+          <t>985126.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>512978</v>
+        <v>520887.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>747665</t>
+          <t>772814</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>102075.7795125219</t>
+          <t>116266.6717958167</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>284361.66221158</t>
+          <t>194316.5793539381</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1250489.0</t>
+          <t>601605.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,127 +5613,127 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>636.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>209.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-28.40</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>-12.18</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>-0.24</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>208.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.26</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-28.15</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>243.0</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>-12.61</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>-1.44</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>57.82</t>
+          <t>82.31</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>203.4</t>
+          <t>205.6</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>216.72</v>
+        <v>215.58</v>
       </c>
       <c r="AN13" t="n">
-        <v>229.4</v>
+        <v>229.23</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>218.13</t>
+          <t>218.24</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.70</t>
+          <t>-137.99</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>235133.4</v>
+        <v>196040.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>327258.2</t>
+          <t>273811.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1062345.88</v>
+        <v>1049433.36</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-92124</t>
+          <t>-77770</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-73662.2362250302</t>
+          <t>-72775.80031441378</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-65403.01296263438</t>
+          <t>-67900.40280602351</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1187.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>57.82</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>203.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>217.92</v>
+        <v>216.72</v>
       </c>
       <c r="AN14" t="n">
-        <v>229.57</v>
+        <v>229.4</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>218.03</t>
+          <t>218.13</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-136.58</t>
+          <t>-137.70</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>261303.6</v>
+        <v>235133.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>360072.2</t>
+          <t>327258.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1087687.9</v>
+        <v>1062345.88</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-98768</t>
+          <t>-92124</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-75163.91318182944</t>
+          <t>-73662.2362250302</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-60756.27700912725</t>
+          <t>-65403.01296263438</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>927.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-27.43</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>219.42</v>
+        <v>217.92</v>
       </c>
       <c r="AN15" t="n">
-        <v>229.64</v>
+        <v>229.57</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>218.03</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.54</t>
+          <t>-136.58</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>277235.2</v>
+        <v>261303.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>364259.9</t>
+          <t>360072.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1109012.44</v>
+        <v>1087687.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-87024</t>
+          <t>-98768</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-77783.48339504802</t>
+          <t>-75163.91318182944</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-62901.108610934</t>
+          <t>-60756.27700912725</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1345.0</t>
+          <t>927.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-23.89</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.10</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>200.9</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>221</v>
+        <v>219.42</v>
       </c>
       <c r="AN16" t="n">
-        <v>229.9</v>
+        <v>229.64</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-55.58</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-131.23</t>
+          <t>-134.54</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>327128.4</v>
+        <v>277235.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>378625.9</t>
+          <t>364259.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1132112.48</v>
+        <v>1109012.44</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-51497</t>
+          <t>-87024</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-80489.36971943239</t>
+          <t>-77783.48339504802</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-57460.89987741027</t>
+          <t>-62901.108610934</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7291,17 +7291,17 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,102 +7358,102 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-13.60</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-16.81</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7.83</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>-1.26</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-10.69</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>243.0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>-16.81</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>-2.27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>223.02</v>
+        <v>221</v>
       </c>
       <c r="AN17" t="n">
-        <v>230.31</v>
+        <v>229.9</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>351582.6</v>
+        <v>327128.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1170503.62</v>
+        <v>1132112.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1651.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>225.2</v>
+        <v>223.02</v>
       </c>
       <c r="AN18" t="n">
-        <v>230.45</v>
+        <v>230.31</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-126.89</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>419383</v>
+        <v>351582.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>393659.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1181679.14</v>
+        <v>1170503.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-42077</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>-84676.36423616367</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-56020.92669104022</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>227.1</v>
+        <v>225.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>230.35</v>
+        <v>230.45</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>458840.8</v>
+        <v>419383</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1187183.2</v>
+        <v>1181679.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>-58569.71761440305</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>229.28</v>
+        <v>227.1</v>
       </c>
       <c r="AN20" t="n">
-        <v>230.34</v>
+        <v>230.35</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>451284.6</v>
+        <v>458840.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1190565.96</v>
+        <v>1187183.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-52095.49631496938</t>
+          <t>-54453.1433044069</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,34 +9204,34 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>230.98</v>
+        <v>229.28</v>
       </c>
       <c r="AN21" t="n">
-        <v>230.29</v>
+        <v>230.34</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>430123.4</v>
+        <v>451284.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1191948.4</v>
+        <v>1190565.96</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-58802.80431880965</t>
+          <t>-52095.49631496938</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>232.15</v>
+        <v>230.98</v>
       </c>
       <c r="AN22" t="n">
-        <v>229.96</v>
+        <v>230.29</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>435737</v>
+        <v>430123.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1189336.42</v>
+        <v>1191948.4</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-61040.46559862403</t>
+          <t>-58802.80431880965</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2120.0</t>
+          <t>3066.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>636</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>225.1</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>233.28</v>
+        <v>232.15</v>
       </c>
       <c r="AN23" t="n">
-        <v>229.57</v>
+        <v>229.96</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>217.69</t>
+          <t>217.77</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-1010.12</t>
+          <t>-305.02</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-101.04</t>
+          <t>-104.38</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>898117.2257142856</t>
+          <t>897120.6954350928</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>379052.8</v>
+        <v>435737</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>373683.5</t>
+          <t>393344.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1181965.28</v>
+        <v>1189336.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-133148.7005222207</t>
+          <t>-122055.1259185904</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-91884.92936983652</t>
+          <t>-61040.46559862403</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>472903.0</t>
+          <t>667498.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>16.39</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>85.17</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5910.0</t>
+          <t>3528.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-45.31</t>
+          <t>-34.49</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1049,38 +1049,38 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>40.98</v>
+        <v>41.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>38.52</v>
+        <v>38.57</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-61.72</t>
+          <t>-75.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-54.86</t>
+          <t>-61.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>235846.0</t>
+          <t>137421.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>207413.4</v>
+        <v>191065.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>379273.5</t>
+          <t>291649.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>543077.08</v>
+        <v>531323.4399999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-171860</t>
+          <t>-100584</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-28227.94494017843</t>
+          <t>-41958.78317699529</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-113655.960797329</t>
+          <t>-117478.393479488</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>235846.0</t>
+          <t>137421.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4049.0</t>
+          <t>5910.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-40.63</t>
+          <t>-45.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>40.83</v>
+        <v>40.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.44</v>
+        <v>38.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-55.91</t>
+          <t>-61.72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-47.89</t>
+          <t>-54.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>246893.2</v>
+        <v>207413.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>415849.4</t>
+          <t>379273.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>548827.92</v>
+        <v>543077.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-168956</t>
+          <t>-171860</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12695.5784206965</t>
+          <t>-28227.94494017843</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-114681.7369371973</t>
+          <t>-113655.960797329</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5712.0</t>
+          <t>4049.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-41.30</t>
+          <t>-40.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>40.74</v>
+        <v>40.83</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.34</v>
+        <v>38.44</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-48.93</t>
+          <t>-55.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-40.61</t>
+          <t>-47.89</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>308262.6</v>
+        <v>246893.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>525128.6</t>
+          <t>415849.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>553146.3199999999</v>
+        <v>548827.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-216866</t>
+          <t>-168956</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5847.359491394556</t>
+          <t>-12695.5784206965</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-103678.2479606807</t>
+          <t>-114681.7369371973</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>34.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5060.0</t>
+          <t>5712.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-58.84</t>
+          <t>-41.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,17 +2304,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>40.69</v>
+        <v>40.74</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.24</v>
+        <v>38.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-33.79</t>
+          <t>-48.93</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-40.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>336685</v>
+        <v>308262.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>817991.7</t>
+          <t>525128.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>553429.1800000001</v>
+        <v>553146.3199999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-481306</t>
+          <t>-216866</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>25761.10630086278</t>
+          <t>5847.359491394556</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-91031.04056706117</t>
+          <t>-103678.2479606807</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-62.77</t>
+          <t>-58.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,176 +2734,176 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>40.56</v>
+        <v>40.69</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.13</v>
+        <v>38.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-33.35</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>378236.0299145299</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>336685</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>817991.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>553429.1800000001</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-481306</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>25761.10630086278</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-91031.04056706117</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>35.27</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-27.71</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>378481.5427960057</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>392234</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>1053458.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>552802.24</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-661224</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>46996.04209503077</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-67837.9214130668</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
           <t>16.66616779909605</t>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10767.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,72 +3048,72 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-3.95</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-62.77</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-3.85</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-52.26</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>40.5</v>
+        <v>40.56</v>
       </c>
       <c r="AN7" t="n">
-        <v>38.03</v>
+        <v>38.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>551133.6</v>
+        <v>392234</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1154537.3</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>552940.5600000001</v>
+        <v>552802.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-603403</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>67874.94455104851</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-33967.36114260822</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10659.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>40.46</v>
+        <v>40.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.94</v>
+        <v>38.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>584805.6</v>
+        <v>551133.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1142553.9</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>554651.52</v>
+        <v>552940.5600000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-557748</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>86391.72740444065</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-7305.190715431352</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-13.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>40.19</v>
+        <v>40.46</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.75</v>
+        <v>37.94</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>741994.6</v>
+        <v>584805.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>550504.28</v>
+        <v>554651.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>27691.05956322944</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.98</v>
+        <v>40.19</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.54</v>
+        <v>37.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1299298.4</v>
+        <v>741994.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>545802.54</v>
+        <v>550504.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87572.0578340583</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-14.66</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.7</v>
+        <v>39.98</v>
       </c>
       <c r="AN11" t="n">
-        <v>37.31</v>
+        <v>37.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1714683.2</v>
+        <v>1299298.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>538423.64</v>
+        <v>545802.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>157331.2318697403</t>
+          <t>87572.0578340583</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13784.0</t>
+          <t>21683.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-19.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>86.56</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.33</v>
+        <v>39.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.04</v>
+        <v>37.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>53.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378481.5427960057</t>
+          <t>378236.0299145299</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1757941</v>
+        <v>1714683.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>985126.9</t>
+          <t>1068516.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>520887.4</v>
+        <v>538423.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>772814</t>
+          <t>646167</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>116266.6717958167</t>
+          <t>122584.2964225742</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>194316.5793539381</t>
+          <t>157331.2318697403</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>601605.0</t>
+          <t>1013660.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>768.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-28.40</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>205.6</t>
+          <t>207.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>215.58</v>
+        <v>214.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>229.23</v>
+        <v>229.02</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>218.24</t>
+          <t>218.32</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.99</t>
+          <t>-137.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>133033.0</t>
+          <t>160881.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>196040.8</v>
+        <v>174850.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>273811.7</t>
+          <t>250989.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1049433.36</v>
+        <v>1027948.98</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-77770</t>
+          <t>-76139</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-72775.80031441378</t>
+          <t>-71712.21036238785</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-67900.40280602351</t>
+          <t>-65862.46562624528</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>133033.0</t>
+          <t>160881.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6043,127 +6043,127 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>636.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>209.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-28.40</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-12.18</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>-0.24</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>208.0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-28.15</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>243.0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>-12.61</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>-1.44</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>57.82</t>
+          <t>82.31</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>203.4</t>
+          <t>205.6</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>216.72</v>
+        <v>215.58</v>
       </c>
       <c r="AN14" t="n">
-        <v>229.4</v>
+        <v>229.23</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>218.13</t>
+          <t>218.24</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.70</t>
+          <t>-137.99</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>235133.4</v>
+        <v>196040.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>327258.2</t>
+          <t>273811.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1062345.88</v>
+        <v>1049433.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-92124</t>
+          <t>-77770</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-73662.2362250302</t>
+          <t>-72775.80031441378</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-65403.01296263438</t>
+          <t>-67900.40280602351</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1187.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>57.82</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>203.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>217.92</v>
+        <v>216.72</v>
       </c>
       <c r="AN15" t="n">
-        <v>229.57</v>
+        <v>229.4</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>218.03</t>
+          <t>218.13</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-136.58</t>
+          <t>-137.70</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>261303.6</v>
+        <v>235133.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>360072.2</t>
+          <t>327258.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1087687.9</v>
+        <v>1062345.88</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-98768</t>
+          <t>-92124</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-75163.91318182944</t>
+          <t>-73662.2362250302</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-60756.27700912725</t>
+          <t>-65403.01296263438</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>927.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-27.43</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>219.42</v>
+        <v>217.92</v>
       </c>
       <c r="AN16" t="n">
-        <v>229.64</v>
+        <v>229.57</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>218.03</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.54</t>
+          <t>-136.58</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>277235.2</v>
+        <v>261303.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>364259.9</t>
+          <t>360072.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1109012.44</v>
+        <v>1087687.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-87024</t>
+          <t>-98768</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-77783.48339504802</t>
+          <t>-75163.91318182944</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-62901.108610934</t>
+          <t>-60756.27700912725</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1345.0</t>
+          <t>927.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-23.89</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.10</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>200.9</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>221</v>
+        <v>219.42</v>
       </c>
       <c r="AN17" t="n">
-        <v>229.9</v>
+        <v>229.64</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-55.58</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-131.23</t>
+          <t>-134.54</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>327128.4</v>
+        <v>277235.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>378625.9</t>
+          <t>364259.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1132112.48</v>
+        <v>1109012.44</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-51497</t>
+          <t>-87024</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-80489.36971943239</t>
+          <t>-77783.48339504802</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-57460.89987741027</t>
+          <t>-62901.108610934</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>223.02</v>
+        <v>221</v>
       </c>
       <c r="AN18" t="n">
-        <v>230.31</v>
+        <v>229.9</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>351582.6</v>
+        <v>327128.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1170503.62</v>
+        <v>1132112.48</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1651.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>225.2</v>
+        <v>223.02</v>
       </c>
       <c r="AN19" t="n">
-        <v>230.45</v>
+        <v>230.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-126.89</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>419383</v>
+        <v>351582.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>393659.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1181679.14</v>
+        <v>1170503.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-42077</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>-84676.36423616367</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-56020.92669104022</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>227.1</v>
+        <v>225.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>230.35</v>
+        <v>230.45</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>458840.8</v>
+        <v>419383</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1187183.2</v>
+        <v>1181679.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>-58569.71761440305</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>229.28</v>
+        <v>227.1</v>
       </c>
       <c r="AN21" t="n">
-        <v>230.34</v>
+        <v>230.35</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>451284.6</v>
+        <v>458840.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1190565.96</v>
+        <v>1187183.2</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-52095.49631496938</t>
+          <t>-54453.1433044069</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,34 +9634,34 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>230.98</v>
+        <v>229.28</v>
       </c>
       <c r="AN22" t="n">
-        <v>230.29</v>
+        <v>230.34</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>430123.4</v>
+        <v>451284.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1191948.4</v>
+        <v>1190565.96</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-58802.80431880965</t>
+          <t>-52095.49631496938</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3066.0</t>
+          <t>1833.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>768</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>232.15</v>
+        <v>230.98</v>
       </c>
       <c r="AN23" t="n">
-        <v>229.96</v>
+        <v>230.29</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>217.77</t>
+          <t>217.91</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-305.02</t>
+          <t>-185.29</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.38</t>
+          <t>-108.16</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/08/26</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>897120.6954350928</t>
+          <t>896186.5085470086</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>435737</v>
+        <v>430123.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>393344.8</t>
+          <t>398138.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1189336.42</v>
+        <v>1191948.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-122055.1259185904</t>
+          <t>-112323.9995186242</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-61040.46559862403</t>
+          <t>-58802.80431880965</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>667498.0</t>
+          <t>389105.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>85.17</t>
+          <t>85.26</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3528.0</t>
+          <t>3724.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.49</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>41.04</v>
+        <v>41.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>38.57</v>
+        <v>38.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-75.05</t>
+          <t>-88.97</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-61.99</t>
+          <t>-68.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>137421.0</t>
+          <t>143439.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>191065.2</v>
+        <v>179066.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>291649.6</t>
+          <t>257875.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>531323.4399999999</v>
+        <v>528903.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-100584</t>
+          <t>-78809</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-41958.78317699529</t>
+          <t>-53467.5529220748</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-117478.393479488</t>
+          <t>-116765.7865200121</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>137421.0</t>
+          <t>143439.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5910.0</t>
+          <t>3528.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-45.31</t>
+          <t>-34.49</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,32 +1444,32 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1479,38 +1479,38 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>40.98</v>
+        <v>41.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.52</v>
+        <v>38.57</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-61.72</t>
+          <t>-75.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-54.86</t>
+          <t>-61.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>235846.0</t>
+          <t>137421.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>207413.4</v>
+        <v>191065.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>379273.5</t>
+          <t>291649.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>543077.08</v>
+        <v>531323.4399999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-171860</t>
+          <t>-100584</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-28227.94494017843</t>
+          <t>-41958.78317699529</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-113655.960797329</t>
+          <t>-117478.393479488</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>235846.0</t>
+          <t>137421.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4049.0</t>
+          <t>5910.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-40.63</t>
+          <t>-45.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>40.83</v>
+        <v>40.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.44</v>
+        <v>38.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-55.91</t>
+          <t>-61.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-47.89</t>
+          <t>-54.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>246893.2</v>
+        <v>207413.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>415849.4</t>
+          <t>379273.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>548827.92</v>
+        <v>543077.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-168956</t>
+          <t>-171860</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12695.5784206965</t>
+          <t>-28227.94494017843</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-114681.7369371973</t>
+          <t>-113655.960797329</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5712.0</t>
+          <t>4049.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-41.30</t>
+          <t>-40.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>40.74</v>
+        <v>40.83</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.34</v>
+        <v>38.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-48.93</t>
+          <t>-55.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-40.61</t>
+          <t>-47.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>308262.6</v>
+        <v>246893.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>525128.6</t>
+          <t>415849.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>553146.3199999999</v>
+        <v>548827.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-216866</t>
+          <t>-168956</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5847.359491394556</t>
+          <t>-12695.5784206965</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-103678.2479606807</t>
+          <t>-114681.7369371973</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>34.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5060.0</t>
+          <t>5712.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-58.84</t>
+          <t>-41.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>40.69</v>
+        <v>40.74</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.24</v>
+        <v>38.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-33.79</t>
+          <t>-48.93</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-40.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>336685</v>
+        <v>308262.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>817991.7</t>
+          <t>525128.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>553429.1800000001</v>
+        <v>553146.3199999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-481306</t>
+          <t>-216866</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>25761.10630086278</t>
+          <t>5847.359491394556</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-91031.04056706117</t>
+          <t>-103678.2479606807</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-62.77</t>
+          <t>-58.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,176 +3164,176 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>40.56</v>
+        <v>40.69</v>
       </c>
       <c r="AN7" t="n">
-        <v>38.13</v>
+        <v>38.24</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-33.35</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>378004.0561877667</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>336685</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>817991.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>553429.1800000001</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-481306</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>25761.10630086278</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-91031.04056706117</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>35.27</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-27.71</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>378236.0299145299</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>392234</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>1053458.6</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>552802.24</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-661224</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>46996.04209503077</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-67837.9214130668</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
           <t>16.66616779909605</t>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10767.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,72 +3478,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-62.77</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.98</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-3.95</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-52.26</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>40.5</v>
+        <v>40.56</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.03</v>
+        <v>38.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>551133.6</v>
+        <v>392234</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1154537.3</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>552940.5600000001</v>
+        <v>552802.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-603403</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>67874.94455104851</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-33967.36114260822</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,14 +3876,14 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10659.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-13.36</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>40.46</v>
+        <v>40.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.94</v>
+        <v>38.03</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>584805.6</v>
+        <v>551133.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1142553.9</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>554651.52</v>
+        <v>552940.5600000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-557748</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>86391.72740444065</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-7305.190715431352</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>40.19</v>
+        <v>40.46</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.75</v>
+        <v>37.94</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>741994.6</v>
+        <v>584805.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>550504.28</v>
+        <v>554651.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>27691.05956322944</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.98</v>
+        <v>40.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>37.54</v>
+        <v>37.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1299298.4</v>
+        <v>741994.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>545802.54</v>
+        <v>550504.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87572.0578340583</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21683.0</t>
+          <t>10817.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-19.2</t>
+          <t>-14.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.7</v>
+        <v>39.98</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.31</v>
+        <v>37.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378236.0299145299</t>
+          <t>378004.0561877667</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1714683.2</v>
+        <v>1299298.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1068516.1</t>
+          <t>1097459.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>538423.64</v>
+        <v>545802.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>646167</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>122584.2964225742</t>
+          <t>117197.7981781871</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>157331.2318697403</t>
+          <t>87572.0578340583</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1013660.0</t>
+          <t>481178.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>768.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>207.8</t>
+          <t>208.7</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>214.32</v>
+        <v>213.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>229.02</v>
+        <v>228.72</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>218.32</t>
+          <t>218.44</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.67</t>
+          <t>-136.90</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>160881.0</t>
+          <t>135722.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>174850.2</v>
+        <v>164277.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>250989.3</t>
+          <t>220756.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1027948.98</v>
+        <v>963448.96</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-76139</t>
+          <t>-56478</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-71712.21036238785</t>
+          <t>-70629.75845428885</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-65862.46562624528</t>
+          <t>-64676.27295974438</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>160881.0</t>
+          <t>135722.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>768.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-28.40</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>205.6</t>
+          <t>207.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>215.58</v>
+        <v>214.32</v>
       </c>
       <c r="AN14" t="n">
-        <v>229.23</v>
+        <v>229.02</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>218.24</t>
+          <t>218.32</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.99</t>
+          <t>-137.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>133033.0</t>
+          <t>160881.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>196040.8</v>
+        <v>174850.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>273811.7</t>
+          <t>250989.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1049433.36</v>
+        <v>1027948.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-77770</t>
+          <t>-76139</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-72775.80031441378</t>
+          <t>-71712.21036238785</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-67900.40280602351</t>
+          <t>-65862.46562624528</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>133033.0</t>
+          <t>160881.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6473,127 +6473,127 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>636.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>209.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-28.40</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-12.18</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>-0.24</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>208.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-28.15</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>243.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>-12.61</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>-1.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>57.82</t>
+          <t>82.31</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>203.4</t>
+          <t>205.6</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>216.72</v>
+        <v>215.58</v>
       </c>
       <c r="AN15" t="n">
-        <v>229.4</v>
+        <v>229.23</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>218.13</t>
+          <t>218.24</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.70</t>
+          <t>-137.99</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>235133.4</v>
+        <v>196040.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>327258.2</t>
+          <t>273811.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1062345.88</v>
+        <v>1049433.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-92124</t>
+          <t>-77770</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-73662.2362250302</t>
+          <t>-72775.80031441378</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-65403.01296263438</t>
+          <t>-67900.40280602351</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.70</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1187.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>57.82</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>203.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>217.92</v>
+        <v>216.72</v>
       </c>
       <c r="AN16" t="n">
-        <v>229.57</v>
+        <v>229.4</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>218.03</t>
+          <t>218.13</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-136.58</t>
+          <t>-137.70</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>261303.6</v>
+        <v>235133.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>360072.2</t>
+          <t>327258.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1087687.9</v>
+        <v>1062345.88</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-98768</t>
+          <t>-92124</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-75163.91318182944</t>
+          <t>-73662.2362250302</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-60756.27700912725</t>
+          <t>-65403.01296263438</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>927.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-27.43</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>219.42</v>
+        <v>217.92</v>
       </c>
       <c r="AN17" t="n">
-        <v>229.64</v>
+        <v>229.57</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>218.03</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-134.54</t>
+          <t>-136.58</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>277235.2</v>
+        <v>261303.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>364259.9</t>
+          <t>360072.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1109012.44</v>
+        <v>1087687.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-87024</t>
+          <t>-98768</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-77783.48339504802</t>
+          <t>-75163.91318182944</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-62901.108610934</t>
+          <t>-60756.27700912725</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1345.0</t>
+          <t>927.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-23.89</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-9.10</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>200.9</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>221</v>
+        <v>219.42</v>
       </c>
       <c r="AN18" t="n">
-        <v>229.9</v>
+        <v>229.64</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-55.58</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-131.23</t>
+          <t>-134.54</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>327128.4</v>
+        <v>277235.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>378625.9</t>
+          <t>364259.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1132112.48</v>
+        <v>1109012.44</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-51497</t>
+          <t>-87024</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-80489.36971943239</t>
+          <t>-77783.48339504802</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-57460.89987741027</t>
+          <t>-62901.108610934</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8151,17 +8151,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>223.02</v>
+        <v>221</v>
       </c>
       <c r="AN19" t="n">
-        <v>230.31</v>
+        <v>229.9</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>351582.6</v>
+        <v>327128.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1170503.62</v>
+        <v>1132112.48</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1651.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>225.2</v>
+        <v>223.02</v>
       </c>
       <c r="AN20" t="n">
-        <v>230.45</v>
+        <v>230.31</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-126.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>419383</v>
+        <v>351582.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>393659.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1181679.14</v>
+        <v>1170503.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-42077</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>-84676.36423616367</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-56020.92669104022</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>227.1</v>
+        <v>225.2</v>
       </c>
       <c r="AN21" t="n">
-        <v>230.35</v>
+        <v>230.45</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>458840.8</v>
+        <v>419383</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1187183.2</v>
+        <v>1181679.14</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>-58569.71761440305</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2122.0</t>
+          <t>1622.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>209.8</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>229.28</v>
+        <v>227.1</v>
       </c>
       <c r="AN22" t="n">
-        <v>230.34</v>
+        <v>230.35</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>217.91</t>
+          <t>217.84</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-143.19</t>
+          <t>-114.15</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-117.78</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>451284.6</v>
+        <v>458840.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>403006.7</t>
+          <t>399885.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1190565.96</v>
+        <v>1187183.2</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-103058.0759488311</t>
+          <t>-95580.3940035351</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-52095.49631496938</t>
+          <t>-54453.1433044069</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>438050.0</t>
+          <t>326648.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1833.0</t>
+          <t>2122.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,34 +10064,34 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>219.1</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>230.98</v>
+        <v>229.28</v>
       </c>
       <c r="AN23" t="n">
-        <v>230.29</v>
+        <v>230.34</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-185.29</t>
+          <t>-143.19</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-108.16</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>896186.5085470086</t>
+          <t>895201.2972972973</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>430123.4</v>
+        <v>451284.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>398138.1</t>
+          <t>403006.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1191948.4</v>
+        <v>1190565.96</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-112323.9995186242</t>
+          <t>-103058.0759488311</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-58802.80431880965</t>
+          <t>-52095.49631496938</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>389105.0</t>
+          <t>438050.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>85.26</t>
+          <t>85.73</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/處理器_IC.xlsx
+++ b/Result/checksun_type/處理器_IC.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3724.0</t>
+          <t>4725.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,79 +898,79 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-28.52</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>39.7</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-30.56</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>36.85</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>38.83</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>41.2</v>
+        <v>41.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>38.63</v>
+        <v>38.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>36.48</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-88.97</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-68.91</t>
+          <t>-75.73</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>143439.0</t>
+          <t>182755.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>179066.4</v>
+        <v>171431.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>257875.7</t>
+          <t>239847.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>528903.2</v>
+        <v>505498</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-78809</t>
+          <t>-68415</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-53467.5529220748</t>
+          <t>-62226.25508566001</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-116765.7865200121</t>
+          <t>-110399.1169853787</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>143439.0</t>
+          <t>182755.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3528.0</t>
+          <t>3724.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.49</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>41.04</v>
+        <v>41.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.57</v>
+        <v>38.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-75.05</t>
+          <t>-88.97</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-61.99</t>
+          <t>-68.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>137421.0</t>
+          <t>143439.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>191065.2</v>
+        <v>179066.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>291649.6</t>
+          <t>257875.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>531323.4399999999</v>
+        <v>528903.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-100584</t>
+          <t>-78809</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-41958.78317699529</t>
+          <t>-53467.5529220748</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-117478.393479488</t>
+          <t>-116765.7865200121</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>137421.0</t>
+          <t>143439.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5910.0</t>
+          <t>3528.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-45.31</t>
+          <t>-34.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,32 +1874,32 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1909,38 +1909,38 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>40.98</v>
+        <v>41.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.52</v>
+        <v>38.57</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-61.72</t>
+          <t>-75.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-54.86</t>
+          <t>-61.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>235846.0</t>
+          <t>137421.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>207413.4</v>
+        <v>191065.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>379273.5</t>
+          <t>291649.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>543077.08</v>
+        <v>531323.4399999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-171860</t>
+          <t>-100584</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-28227.94494017843</t>
+          <t>-41958.78317699529</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-113655.960797329</t>
+          <t>-117478.393479488</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>235846.0</t>
+          <t>137421.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4049.0</t>
+          <t>5910.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-40.63</t>
+          <t>-45.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>40.83</v>
+        <v>40.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.44</v>
+        <v>38.52</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-55.91</t>
+          <t>-61.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-47.89</t>
+          <t>-54.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>246893.2</v>
+        <v>207413.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>415849.4</t>
+          <t>379273.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>548827.92</v>
+        <v>543077.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-168956</t>
+          <t>-171860</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12695.5784206965</t>
+          <t>-28227.94494017843</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-114681.7369371973</t>
+          <t>-113655.960797329</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>157697.0</t>
+          <t>235846.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5712.0</t>
+          <t>4049.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-41.30</t>
+          <t>-40.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>40.74</v>
+        <v>40.83</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.34</v>
+        <v>38.44</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-48.93</t>
+          <t>-55.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-40.61</t>
+          <t>-47.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>308262.6</v>
+        <v>246893.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>525128.6</t>
+          <t>415849.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>553146.3199999999</v>
+        <v>548827.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-216866</t>
+          <t>-168956</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5847.359491394556</t>
+          <t>-12695.5784206965</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-103678.2479606807</t>
+          <t>-114681.7369371973</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>220929.0</t>
+          <t>157697.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>34.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5060.0</t>
+          <t>5712.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-58.84</t>
+          <t>-41.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>40.69</v>
+        <v>40.74</v>
       </c>
       <c r="AN7" t="n">
-        <v>38.24</v>
+        <v>38.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-33.79</t>
+          <t>-48.93</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-40.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>336685</v>
+        <v>308262.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>817991.7</t>
+          <t>525128.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>553429.1800000001</v>
+        <v>553146.3199999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-481306</t>
+          <t>-216866</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>25761.10630086278</t>
+          <t>5847.359491394556</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-91031.04056706117</t>
+          <t>-103678.2479606807</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>203433.0</t>
+          <t>220929.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-62.77</t>
+          <t>-58.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,176 +3594,176 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>40.56</v>
+        <v>40.69</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.13</v>
+        <v>38.24</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-33.79</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-33.35</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>377856.5113636364</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>336685</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>817991.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>553429.1800000001</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-481306</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>25761.10630086278</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-91031.04056706117</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>35.27</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-27.71</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>378004.0561877667</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>392234</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>1053458.6</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>552802.24</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-661224</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>46996.04209503077</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-67837.9214130668</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>219162.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>16.66616779909605</t>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10767.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,72 +3908,72 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-62.77</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.85</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-52.26</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>40.5</v>
+        <v>40.56</v>
       </c>
       <c r="AN9" t="n">
-        <v>38.03</v>
+        <v>38.13</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-27.71</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>551133.6</v>
+        <v>392234</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1154537.3</t>
+          <t>1053458.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>552940.5600000001</v>
+        <v>552802.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-603403</t>
+          <t>-661224</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>67874.94455104851</t>
+          <t>46996.04209503077</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-33967.36114260822</t>
+          <t>-67837.9214130668</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>433245.0</t>
+          <t>219162.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10659.0</t>
+          <t>10767.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-52.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>40.46</v>
+        <v>40.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.94</v>
+        <v>38.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>584805.6</v>
+        <v>551133.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1142553.9</t>
+          <t>1154537.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>554651.52</v>
+        <v>552940.5600000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-557748</t>
+          <t>-603403</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>86391.72740444065</t>
+          <t>67874.94455104851</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-7305.190715431352</t>
+          <t>-33967.36114260822</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>464544.0</t>
+          <t>433245.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8393.0</t>
+          <t>10659.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-14.7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.80</t>
+          <t>-48.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>40.19</v>
+        <v>40.46</v>
       </c>
       <c r="AN11" t="n">
-        <v>37.75</v>
+        <v>37.94</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>741994.6</v>
+        <v>584805.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1120906.4</t>
+          <t>1142553.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>550504.28</v>
+        <v>554651.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-378911</t>
+          <t>-557748</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>103427.5306989628</t>
+          <t>86391.72740444065</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>27691.05956322944</t>
+          <t>-7305.190715431352</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>363041.0</t>
+          <t>464544.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10817.0</t>
+          <t>8393.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14.51</t>
+          <t>-11.81</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.98</v>
+        <v>40.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.54</v>
+        <v>37.75</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>378004.0561877667</t>
+          <t>377856.5113636364</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1299298.4</v>
+        <v>741994.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1097459.1</t>
+          <t>1120906.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>545802.54</v>
+        <v>550504.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>-378911</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>117197.7981781871</t>
+          <t>103427.5306989628</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87572.0578340583</t>
+          <t>27691.05956322944</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>481178.0</t>
+          <t>363041.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.72</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>547.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>207.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>648.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>209.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-30.96</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.18</t>
+          <t>-12.82</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>208.7</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>213.3</v>
+        <v>212.02</v>
       </c>
       <c r="AN13" t="n">
-        <v>228.72</v>
+        <v>228.12</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>218.44</t>
+          <t>218.48</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-136.90</t>
+          <t>-135.93</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>135722.0</t>
+          <t>114406.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>164277.8</v>
+        <v>137761</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>220756.5</t>
+          <t>199532.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>963448.96</v>
+        <v>885427.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-56478</t>
+          <t>-61771</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-70629.75845428885</t>
+          <t>-69583.29273350598</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-64676.27295974438</t>
+          <t>-63827.73126920016</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>135722.0</t>
+          <t>114406.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.70</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>768.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>207.8</t>
+          <t>208.7</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>214.32</v>
+        <v>213.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>229.02</v>
+        <v>228.72</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>218.32</t>
+          <t>218.44</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.67</t>
+          <t>-136.90</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>160881.0</t>
+          <t>135722.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>174850.2</v>
+        <v>164277.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>250989.3</t>
+          <t>220756.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1027948.98</v>
+        <v>963448.96</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-76139</t>
+          <t>-56478</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-71712.21036238785</t>
+          <t>-70629.75845428885</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-65862.46562624528</t>
+          <t>-64676.27295974438</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>160881.0</t>
+          <t>135722.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>768.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.40</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>205.6</t>
+          <t>207.8</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>215.58</v>
+        <v>214.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>229.23</v>
+        <v>229.02</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>218.24</t>
+          <t>218.32</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.99</t>
+          <t>-137.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>133033.0</t>
+          <t>160881.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>196040.8</v>
+        <v>174850.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>273811.7</t>
+          <t>250989.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1049433.36</v>
+        <v>1027948.98</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-77770</t>
+          <t>-76139</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-72775.80031441378</t>
+          <t>-71712.21036238785</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-67900.40280602351</t>
+          <t>-65862.46562624528</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>133033.0</t>
+          <t>160881.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6903,127 +6903,127 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>636.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>209.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.72</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-28.40</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-12.18</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>-0.24</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>208.0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-28.15</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>243.0</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>-12.61</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-1.44</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>57.82</t>
+          <t>82.31</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>203.4</t>
+          <t>205.6</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>216.72</v>
+        <v>215.58</v>
       </c>
       <c r="AN16" t="n">
-        <v>229.4</v>
+        <v>229.23</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>218.13</t>
+          <t>218.24</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-137.70</t>
+          <t>-137.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>235133.4</v>
+        <v>196040.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>327258.2</t>
+          <t>273811.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1062345.88</v>
+        <v>1049433.36</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-92124</t>
+          <t>-77770</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-73662.2362250302</t>
+          <t>-72775.80031441378</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-65403.01296263438</t>
+          <t>-67900.40280602351</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>144763.0</t>
+          <t>133033.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.70</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1187.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>57.82</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>203.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>217.92</v>
+        <v>216.72</v>
       </c>
       <c r="AN17" t="n">
-        <v>229.57</v>
+        <v>229.4</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>218.03</t>
+          <t>218.13</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-136.58</t>
+          <t>-137.70</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>261303.6</v>
+        <v>235133.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>360072.2</t>
+          <t>327258.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1087687.9</v>
+        <v>1062345.88</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-98768</t>
+          <t>-92124</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-75163.91318182944</t>
+          <t>-73662.2362250302</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-60756.27700912725</t>
+          <t>-65403.01296263438</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>246990.0</t>
+          <t>144763.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>927.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-27.43</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>219.42</v>
+        <v>217.92</v>
       </c>
       <c r="AN18" t="n">
-        <v>229.64</v>
+        <v>229.57</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>218.03</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-134.54</t>
+          <t>-136.58</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>277235.2</v>
+        <v>261303.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>364259.9</t>
+          <t>360072.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1109012.44</v>
+        <v>1087687.9</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-87024</t>
+          <t>-98768</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-77783.48339504802</t>
+          <t>-75163.91318182944</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-62901.108610934</t>
+          <t>-60756.27700912725</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>188584.0</t>
+          <t>246990.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1345.0</t>
+          <t>927.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-23.89</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-9.10</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>200.9</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>221</v>
+        <v>219.42</v>
       </c>
       <c r="AN19" t="n">
-        <v>229.9</v>
+        <v>229.64</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-55.58</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-131.23</t>
+          <t>-134.54</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>327128.4</v>
+        <v>277235.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>378625.9</t>
+          <t>364259.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1132112.48</v>
+        <v>1109012.44</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-51497</t>
+          <t>-87024</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-80489.36971943239</t>
+          <t>-77783.48339504802</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-57460.89987741027</t>
+          <t>-62901.108610934</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>266834.0</t>
+          <t>188584.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1651.0</t>
+          <t>1345.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-9.10</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>223.02</v>
+        <v>221</v>
       </c>
       <c r="AN20" t="n">
-        <v>230.31</v>
+        <v>229.9</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-68.34</t>
+          <t>-55.58</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-126.89</t>
+          <t>-131.23</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>351582.6</v>
+        <v>327128.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>393659.8</t>
+          <t>378625.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1170503.62</v>
+        <v>1132112.48</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-42077</t>
+          <t>-51497</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-84676.36423616367</t>
+          <t>-80489.36971943239</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-56020.92669104022</t>
+          <t>-57460.89987741027</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>328496.0</t>
+          <t>266834.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1651.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>225.2</v>
+        <v>223.02</v>
       </c>
       <c r="AN21" t="n">
-        <v>230.45</v>
+        <v>230.31</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-122.30</t>
+          <t>-126.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>419383</v>
+        <v>351582.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>399217.9</t>
+          <t>393659.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1181679.14</v>
+        <v>1170503.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>-42077</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-89886.44378982249</t>
+          <t>-84676.36423616367</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-58569.71761440305</t>
+          <t>-56020.92669104022</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>275614.0</t>
+          <t>328496.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>85.73</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>227.1</v>
+        <v>225.2</v>
       </c>
       <c r="AN22" t="n">
-        <v>230.35</v>
+        <v>230.45</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>217.84</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-114.15</t>
+          <t>-81.07</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-117.78</t>
+          <t>-122.30</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>895201.2972972973</t>
+          <t>894173.4673295454</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>458840.8</v>
+        <v>419383</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>399885.8</t>
+          <t>399217.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1187183.2</v>
+        <v>1181679.14</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-95580.3940035351</t>
+          <t>-89886.44378982249</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-54453.1433044069</t>
+          <t>-58569.71761440305</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>326648.0</t>
+          <t>275614.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分